--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ.xlsx
@@ -170,7 +170,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -180,12 +180,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -236,17 +230,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="36">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,73 +46,64 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
-    <t>Час</t>
-  </si>
-  <si>
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>1147 Варна Ситроен</t>
-  </si>
-  <si>
-    <t>1146 Варна Сливница</t>
+    <t>Варна</t>
+  </si>
+  <si>
+    <t>Варна Сливница</t>
+  </si>
+  <si>
+    <t>Варна Чайка</t>
+  </si>
+  <si>
+    <t>В4601ХК</t>
+  </si>
+  <si>
+    <t>ТубаДДД2</t>
+  </si>
+  <si>
+    <t>В8262ВР</t>
+  </si>
+  <si>
+    <t>В4602ХК</t>
+  </si>
+  <si>
+    <t>ТубаДДД5</t>
+  </si>
+  <si>
+    <t>ТубаДДД1</t>
   </si>
   <si>
     <t>В4603ХК</t>
   </si>
   <si>
-    <t>В4601ХК</t>
-  </si>
-  <si>
-    <t>В4602ХК</t>
+    <t>78970155027720386</t>
+  </si>
+  <si>
+    <t>78970155027720444</t>
+  </si>
+  <si>
+    <t>78970155027720428</t>
+  </si>
+  <si>
+    <t>78970155027720394</t>
+  </si>
+  <si>
+    <t>78970155027720477</t>
+  </si>
+  <si>
+    <t>78970155027720436</t>
   </si>
   <si>
     <t>78970155027720402</t>
   </si>
   <si>
-    <t>78970155027720386</t>
-  </si>
-  <si>
-    <t>78970155027720394</t>
-  </si>
-  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>12:30:00</t>
-  </si>
-  <si>
-    <t>07:57:00</t>
-  </si>
-  <si>
-    <t>08:22:00</t>
-  </si>
-  <si>
-    <t>10:36:00</t>
-  </si>
-  <si>
-    <t>12:46:00</t>
-  </si>
-  <si>
-    <t>3232097635 3232097635</t>
-  </si>
-  <si>
-    <t>3232146889 3232146889</t>
-  </si>
-  <si>
-    <t>3232229529 3232229529</t>
-  </si>
-  <si>
-    <t>3232567183 3232567183</t>
-  </si>
-  <si>
-    <t>3232570102 3232570102</t>
+    <t>DIESEL EKONOMY</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ</t>
@@ -535,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -544,17 +532,14 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -588,307 +573,343 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46174</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2">
+        <v>27</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="H2">
+        <v>41.58</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="J2">
+        <v>42.39</v>
+      </c>
+      <c r="K2">
+        <v>2781</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3">
+        <v>46174</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="H3">
+        <v>7.7</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="J3">
+        <v>7.85</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="3">
+        <v>46175</v>
+      </c>
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4">
+        <v>56</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.66</v>
+      </c>
+      <c r="H4">
+        <v>92.95999999999999</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.69</v>
+      </c>
+      <c r="J4">
+        <v>94.64</v>
+      </c>
+      <c r="K4">
+        <v>53811</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="3">
+        <v>46183</v>
+      </c>
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46161</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2">
-        <v>30</v>
-      </c>
-      <c r="G2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2">
-        <v>1.52</v>
-      </c>
-      <c r="I2" s="1">
-        <v>45.6</v>
-      </c>
-      <c r="J2">
-        <v>1.55</v>
-      </c>
-      <c r="K2" s="1">
-        <v>46.5</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
         <v>24</v>
       </c>
-      <c r="M2">
-        <v>3033</v>
-      </c>
-      <c r="N2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="3">
-        <v>46162</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3">
-        <v>37</v>
-      </c>
-      <c r="G3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3">
-        <v>1.54</v>
-      </c>
-      <c r="I3" s="1">
-        <v>56.98</v>
-      </c>
-      <c r="J3">
-        <v>1.57</v>
-      </c>
-      <c r="K3" s="1">
-        <v>58.09</v>
-      </c>
-      <c r="L3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M3">
-        <v>2500</v>
-      </c>
-      <c r="N3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="3">
-        <v>46164</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4">
-        <v>40.02</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4">
-        <v>1.54</v>
-      </c>
-      <c r="I4" s="1">
-        <v>61.63</v>
-      </c>
-      <c r="J4">
-        <v>1.57</v>
-      </c>
-      <c r="K4" s="1">
-        <v>62.83</v>
-      </c>
-      <c r="L4" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4">
-        <v>2838</v>
-      </c>
-      <c r="N4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="3">
-        <v>46171</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F5">
-        <v>22.59</v>
-      </c>
-      <c r="G5" t="s">
-        <v>23</v>
+        <v>26.11</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1.53</v>
       </c>
       <c r="H5">
-        <v>1.54</v>
+        <v>39.95</v>
       </c>
       <c r="I5" s="1">
-        <v>34.79</v>
+        <v>1.56</v>
       </c>
       <c r="J5">
-        <v>1.57</v>
-      </c>
-      <c r="K5" s="1">
-        <v>35.47</v>
-      </c>
-      <c r="L5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M5">
-        <v>3262</v>
-      </c>
-      <c r="N5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>40.73</v>
+      </c>
+      <c r="K5">
+        <v>3370</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="3">
-        <v>46171</v>
+        <v>46183</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F6">
-        <v>22.75</v>
-      </c>
-      <c r="G6" t="s">
-        <v>23</v>
+        <v>15</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1.6</v>
       </c>
       <c r="H6">
-        <v>1.54</v>
+        <v>24</v>
       </c>
       <c r="I6" s="1">
-        <v>35.04</v>
+        <v>1.63</v>
       </c>
       <c r="J6">
-        <v>1.57</v>
-      </c>
-      <c r="K6" s="1">
-        <v>35.72</v>
-      </c>
-      <c r="L6" t="s">
+        <v>24.45</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="3">
+        <v>46183</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
         <v>28</v>
       </c>
-      <c r="M6">
-        <v>3070</v>
-      </c>
-      <c r="N6" t="s">
+      <c r="F7">
+        <v>5</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="H7">
+        <v>7.65</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="J7">
+        <v>7.8</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="3">
+        <v>46185</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8">
+        <v>40.32</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="H8">
+        <v>61.69</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="J8">
+        <v>62.9</v>
+      </c>
+      <c r="K8">
+        <v>3689</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="4" t="s">
+      <c r="D12" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="5" t="s">
+      <c r="E12" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="7">
+        <v>103.43</v>
+      </c>
+      <c r="C13" s="7">
+        <v>5</v>
+      </c>
+      <c r="D13" s="8">
+        <v>1.5331</v>
+      </c>
+      <c r="E13" s="7">
+        <v>158.57</v>
+      </c>
+      <c r="F13" s="7">
+        <v>161.67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="7">
+        <v>71</v>
+      </c>
+      <c r="C14" s="7">
+        <v>2</v>
+      </c>
+      <c r="D14" s="8">
+        <v>1.6473</v>
+      </c>
+      <c r="E14" s="7">
+        <v>116.96</v>
+      </c>
+      <c r="F14" s="7">
+        <v>119.09</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="7">
-        <v>152.36</v>
-      </c>
-      <c r="C11" s="7">
-        <v>5</v>
-      </c>
-      <c r="D11" s="8">
-        <v>1.5361</v>
-      </c>
-      <c r="E11" s="7">
-        <v>234.04</v>
-      </c>
-      <c r="F11" s="7">
-        <v>238.61</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="10">
-        <v>152.36</v>
-      </c>
-      <c r="C12" s="10">
-        <v>5</v>
-      </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="10">
-        <v>234.04</v>
-      </c>
-      <c r="F12" s="10">
-        <v>238.61</v>
+      <c r="B15" s="10">
+        <v>174.43</v>
+      </c>
+      <c r="C15" s="10">
+        <v>7</v>
+      </c>
+      <c r="D15" s="8"/>
+      <c r="E15" s="10">
+        <v>275.53</v>
+      </c>
+      <c r="F15" s="10">
+        <v>280.76</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A11:F11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="45">
   <si>
     <t>Дата</t>
   </si>
@@ -46,10 +46,16 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
+    <t>Час</t>
+  </si>
+  <si>
     <t>Километри</t>
   </si>
   <si>
-    <t>Варна</t>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>Варна Цар Освободител</t>
   </si>
   <si>
     <t>Варна Сливница</t>
@@ -104,6 +110,27 @@
   </si>
   <si>
     <t>DIESEL EKONOMY</t>
+  </si>
+  <si>
+    <t>17:56</t>
+  </si>
+  <si>
+    <t>17:57</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>09:19</t>
+  </si>
+  <si>
+    <t>09:20</t>
+  </si>
+  <si>
+    <t>09:21</t>
+  </si>
+  <si>
+    <t>16:21</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ</t>
@@ -523,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -536,10 +563,12 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -573,22 +602,28 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46174</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F2">
         <v>27</v>
@@ -605,25 +640,31 @@
       <c r="J2">
         <v>42.39</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2">
         <v>2781</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="M2">
+        <v>271662</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46174</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -640,25 +681,31 @@
       <c r="J3">
         <v>7.85</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="M3">
+        <v>271664</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46175</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F4">
         <v>56</v>
@@ -675,25 +722,31 @@
       <c r="J4">
         <v>94.64</v>
       </c>
-      <c r="K4">
-        <v>53811</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="K4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4">
+        <v>187892</v>
+      </c>
+      <c r="M4">
+        <v>137793</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
         <v>46183</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F5">
         <v>26.11</v>
@@ -710,25 +763,31 @@
       <c r="J5">
         <v>40.73</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="s">
+        <v>35</v>
+      </c>
+      <c r="L5">
         <v>3370</v>
       </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="M5">
+        <v>110548</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="3">
         <v>46183</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F6">
         <v>15</v>
@@ -745,25 +804,31 @@
       <c r="J6">
         <v>24.45</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="s">
+        <v>36</v>
+      </c>
+      <c r="L6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="M6">
+        <v>110550</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="3">
         <v>46183</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -780,25 +845,31 @@
       <c r="J7">
         <v>7.8</v>
       </c>
-      <c r="K7">
+      <c r="K7" t="s">
+        <v>37</v>
+      </c>
+      <c r="L7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="M7">
+        <v>110554</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="3">
         <v>46185</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F8">
         <v>40.32</v>
@@ -815,13 +886,19 @@
       <c r="J8">
         <v>62.9</v>
       </c>
-      <c r="K8">
+      <c r="K8" t="s">
+        <v>38</v>
+      </c>
+      <c r="L8">
         <v>3689</v>
       </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="M8">
+        <v>274737</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="4" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -829,18 +906,18 @@
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:13">
       <c r="A12" s="5" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>7</v>
@@ -849,9 +926,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:13">
       <c r="A13" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B13" s="7">
         <v>103.43</v>
@@ -869,9 +946,9 @@
         <v>161.67</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:13">
       <c r="A14" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B14" s="7">
         <v>71</v>
@@ -889,9 +966,9 @@
         <v>119.09</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:13">
       <c r="A15" s="9" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B15" s="10">
         <v>174.43</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="42">
   <si>
     <t>Дата</t>
   </si>
@@ -49,88 +49,79 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Километри</t>
-  </si>
-  <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>Варна Цар Освободител</t>
-  </si>
-  <si>
     <t>Варна Сливница</t>
   </si>
   <si>
+    <t>Варна</t>
+  </si>
+  <si>
     <t>Варна Чайка</t>
   </si>
   <si>
+    <t>Варна Варненчик</t>
+  </si>
+  <si>
+    <t>ТубаДДД5</t>
+  </si>
+  <si>
+    <t>ТубаДДД1</t>
+  </si>
+  <si>
     <t>В4601ХК</t>
   </si>
   <si>
-    <t>ТубаДДД2</t>
+    <t>В4602ХК</t>
   </si>
   <si>
     <t>В8262ВР</t>
   </si>
   <si>
-    <t>В4602ХК</t>
-  </si>
-  <si>
-    <t>ТубаДДД5</t>
-  </si>
-  <si>
-    <t>ТубаДДД1</t>
-  </si>
-  <si>
-    <t>В4603ХК</t>
+    <t>ТубаДДД6</t>
+  </si>
+  <si>
+    <t>78970155027720477</t>
+  </si>
+  <si>
+    <t>78970155027720436</t>
   </si>
   <si>
     <t>78970155027720386</t>
   </si>
   <si>
-    <t>78970155027720444</t>
+    <t>78970155027720394</t>
   </si>
   <si>
     <t>78970155027720428</t>
   </si>
   <si>
-    <t>78970155027720394</t>
-  </si>
-  <si>
-    <t>78970155027720477</t>
-  </si>
-  <si>
-    <t>78970155027720436</t>
-  </si>
-  <si>
-    <t>78970155027720402</t>
+    <t>78970155027720485</t>
+  </si>
+  <si>
+    <t>DIESEL EKONOMY</t>
   </si>
   <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>DIESEL EKONOMY</t>
-  </si>
-  <si>
-    <t>17:56</t>
-  </si>
-  <si>
-    <t>17:57</t>
-  </si>
-  <si>
-    <t>14:05</t>
-  </si>
-  <si>
-    <t>09:19</t>
-  </si>
-  <si>
-    <t>09:20</t>
-  </si>
-  <si>
-    <t>09:21</t>
-  </si>
-  <si>
-    <t>16:21</t>
+    <t>2026-06-19 10:59:03</t>
+  </si>
+  <si>
+    <t>2026-06-19 10:59:19</t>
+  </si>
+  <si>
+    <t>2026-06-22 10:27:20</t>
+  </si>
+  <si>
+    <t>2026-06-22 11:36:35</t>
+  </si>
+  <si>
+    <t>2026-06-22 13:39:31</t>
+  </si>
+  <si>
+    <t>2026-06-22 13:40:52</t>
+  </si>
+  <si>
+    <t>2026-06-24 11:03:17</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ</t>
@@ -550,7 +541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -563,12 +554,10 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -602,303 +591,255 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46192</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2">
+        <v>12.23</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="H2">
+        <v>18.71</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="J2">
+        <v>19.08</v>
+      </c>
+      <c r="K2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3">
+        <v>46192</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3">
+        <v>5.17</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="H3">
+        <v>7.81</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="J3">
+        <v>7.96</v>
+      </c>
+      <c r="K3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="3">
+        <v>46195</v>
+      </c>
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="3">
-        <v>46174</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4">
+        <v>37</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.48</v>
+      </c>
+      <c r="H4">
+        <v>54.76</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="J4">
+        <v>55.87</v>
+      </c>
+      <c r="K4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="3">
+        <v>46195</v>
+      </c>
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2">
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5">
+        <v>40.39</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1.48</v>
+      </c>
+      <c r="H5">
+        <v>59.78</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="J5">
+        <v>60.99</v>
+      </c>
+      <c r="K5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="3">
+        <v>46195</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="H2">
-        <v>41.58</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.57</v>
-      </c>
-      <c r="J2">
-        <v>42.39</v>
-      </c>
-      <c r="K2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L2">
-        <v>2781</v>
-      </c>
-      <c r="M2">
-        <v>271662</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="3">
-        <v>46174</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="H3">
-        <v>7.7</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.57</v>
-      </c>
-      <c r="J3">
-        <v>7.85</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="F6">
+        <v>53</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="H6">
+        <v>78.97</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="J6">
+        <v>80.56</v>
+      </c>
+      <c r="K6" t="s">
         <v>33</v>
       </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>271664</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="3">
-        <v>46175</v>
-      </c>
-      <c r="B4" t="s">
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="3">
+        <v>46195</v>
+      </c>
+      <c r="B7" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4">
-        <v>56</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.66</v>
-      </c>
-      <c r="H4">
-        <v>92.95999999999999</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="J4">
-        <v>94.64</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7">
+        <v>19</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="H7">
+        <v>28.31</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="J7">
+        <v>28.88</v>
+      </c>
+      <c r="K7" t="s">
         <v>34</v>
       </c>
-      <c r="L4">
-        <v>187892</v>
-      </c>
-      <c r="M4">
-        <v>137793</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="3">
-        <v>46183</v>
-      </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="3">
+        <v>46197</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8">
         <v>15</v>
       </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5">
-        <v>26.11</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="H5">
-        <v>39.95</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J5">
-        <v>40.73</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="G8" s="1">
+        <v>1.48</v>
+      </c>
+      <c r="H8">
+        <v>22.2</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="J8">
+        <v>22.65</v>
+      </c>
+      <c r="K8" t="s">
         <v>35</v>
       </c>
-      <c r="L5">
-        <v>3370</v>
-      </c>
-      <c r="M5">
-        <v>110548</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="3">
-        <v>46183</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6">
-        <v>15</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1.6</v>
-      </c>
-      <c r="H6">
-        <v>24</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="J6">
-        <v>24.45</v>
-      </c>
-      <c r="K6" t="s">
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="4" t="s">
         <v>36</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>110550</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="3">
-        <v>46183</v>
-      </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="H7">
-        <v>7.65</v>
-      </c>
-      <c r="I7" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J7">
-        <v>7.8</v>
-      </c>
-      <c r="K7" t="s">
-        <v>37</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>110554</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="3">
-        <v>46185</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8">
-        <v>40.32</v>
-      </c>
-      <c r="G8" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="H8">
-        <v>61.69</v>
-      </c>
-      <c r="I8" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J8">
-        <v>62.9</v>
-      </c>
-      <c r="K8" t="s">
-        <v>38</v>
-      </c>
-      <c r="L8">
-        <v>3689</v>
-      </c>
-      <c r="M8">
-        <v>274737</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="4" t="s">
-        <v>39</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -906,18 +847,18 @@
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:11">
       <c r="A12" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>40</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>43</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>7</v>
@@ -926,62 +867,62 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:11">
       <c r="A13" s="6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B13" s="7">
-        <v>103.43</v>
+        <v>99.23</v>
       </c>
       <c r="C13" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D13" s="8">
-        <v>1.5331</v>
+        <v>1.4934</v>
       </c>
       <c r="E13" s="7">
-        <v>158.57</v>
+        <v>148.19</v>
       </c>
       <c r="F13" s="7">
-        <v>161.67</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+        <v>151.17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B14" s="7">
-        <v>71</v>
+        <v>82.56</v>
       </c>
       <c r="C14" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" s="8">
-        <v>1.6473</v>
+        <v>1.482</v>
       </c>
       <c r="E14" s="7">
-        <v>116.96</v>
+        <v>122.35</v>
       </c>
       <c r="F14" s="7">
-        <v>119.09</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+        <v>124.82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B15" s="10">
-        <v>174.43</v>
+        <v>181.79</v>
       </c>
       <c r="C15" s="10">
         <v>7</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="10">
-        <v>275.53</v>
+        <v>270.54</v>
       </c>
       <c r="F15" s="10">
-        <v>280.76</v>
+        <v>275.99</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="79">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,16 +52,22 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Варна Сливница</t>
-  </si>
-  <si>
-    <t>Варна</t>
-  </si>
-  <si>
-    <t>Варна Чайка</t>
-  </si>
-  <si>
-    <t>Варна Варненчик</t>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
   </si>
   <si>
     <t>ТубаДДД5</t>
@@ -67,16 +76,28 @@
     <t>ТубаДДД1</t>
   </si>
   <si>
+    <t>ТубаДДД6</t>
+  </si>
+  <si>
+    <t>В8262ВР</t>
+  </si>
+  <si>
+    <t>В4602ХК</t>
+  </si>
+  <si>
     <t>В4601ХК</t>
   </si>
   <si>
-    <t>В4602ХК</t>
-  </si>
-  <si>
-    <t>В8262ВР</t>
-  </si>
-  <si>
-    <t>ТубаДДД6</t>
+    <t>ТубаДДД4</t>
+  </si>
+  <si>
+    <t>В4603ХК</t>
+  </si>
+  <si>
+    <t>ТубаДДД3</t>
+  </si>
+  <si>
+    <t>В2658НА</t>
   </si>
   <si>
     <t>78970155027720477</t>
@@ -85,16 +106,28 @@
     <t>78970155027720436</t>
   </si>
   <si>
+    <t>78970155027720485</t>
+  </si>
+  <si>
+    <t>78970155027720428</t>
+  </si>
+  <si>
+    <t>78970155027720394</t>
+  </si>
+  <si>
     <t>78970155027720386</t>
   </si>
   <si>
-    <t>78970155027720394</t>
-  </si>
-  <si>
-    <t>78970155027720428</t>
-  </si>
-  <si>
-    <t>78970155027720485</t>
+    <t>78970155027720469</t>
+  </si>
+  <si>
+    <t>78970155027720402</t>
+  </si>
+  <si>
+    <t>78970155027720451</t>
+  </si>
+  <si>
+    <t>78970155027720410</t>
   </si>
   <si>
     <t>DIESEL EKONOMY</t>
@@ -103,25 +136,103 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>2026-06-19 10:59:03</t>
-  </si>
-  <si>
-    <t>2026-06-19 10:59:19</t>
-  </si>
-  <si>
-    <t>2026-06-22 10:27:20</t>
-  </si>
-  <si>
-    <t>2026-06-22 11:36:35</t>
-  </si>
-  <si>
-    <t>2026-06-22 13:39:31</t>
-  </si>
-  <si>
-    <t>2026-06-22 13:40:52</t>
-  </si>
-  <si>
-    <t>2026-06-24 11:03:17</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>10:59:00</t>
+  </si>
+  <si>
+    <t>13:41:00</t>
+  </si>
+  <si>
+    <t>13:39:00</t>
+  </si>
+  <si>
+    <t>11:36:00</t>
+  </si>
+  <si>
+    <t>10:28:00</t>
+  </si>
+  <si>
+    <t>11:02:00</t>
+  </si>
+  <si>
+    <t>05:47:00</t>
+  </si>
+  <si>
+    <t>07:06:00</t>
+  </si>
+  <si>
+    <t>06:05:00</t>
+  </si>
+  <si>
+    <t>06:04:00</t>
+  </si>
+  <si>
+    <t>17:35:00</t>
+  </si>
+  <si>
+    <t>11:06:00</t>
+  </si>
+  <si>
+    <t>14:04:00</t>
+  </si>
+  <si>
+    <t>09:02:00</t>
+  </si>
+  <si>
+    <t>12:52:00</t>
+  </si>
+  <si>
+    <t>3233569167 3233569167</t>
+  </si>
+  <si>
+    <t>3233569168 3233569168</t>
+  </si>
+  <si>
+    <t>3233717171 3233717171</t>
+  </si>
+  <si>
+    <t>3233717942 3233717942</t>
+  </si>
+  <si>
+    <t>3233720228 3233720228</t>
+  </si>
+  <si>
+    <t>3233726352 3233726352</t>
+  </si>
+  <si>
+    <t>3233809271 3233809271</t>
+  </si>
+  <si>
+    <t>3233877529 3233877529</t>
+  </si>
+  <si>
+    <t>3234037053 3234037053</t>
+  </si>
+  <si>
+    <t>3234029542 3234029542</t>
+  </si>
+  <si>
+    <t>3234045264 3234045264</t>
+  </si>
+  <si>
+    <t>3234046101 3234046101</t>
+  </si>
+  <si>
+    <t>3234109358 3234109358</t>
+  </si>
+  <si>
+    <t>3234101045 3234101045</t>
+  </si>
+  <si>
+    <t>3234108455 3234108455</t>
+  </si>
+  <si>
+    <t>3234104146 3234104146</t>
+  </si>
+  <si>
+    <t>3234114612 3234114612</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ</t>
@@ -541,7 +652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -550,14 +661,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -591,343 +705,855 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46192</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F2">
         <v>12.23</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2">
         <v>1.53</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>18.71</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.56</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>19.08</v>
       </c>
-      <c r="K2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46192</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F3">
         <v>5.17</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3">
         <v>1.51</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>7.81</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.54</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>7.96</v>
       </c>
-      <c r="K3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46195</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F4">
-        <v>37</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.48</v>
+        <v>19</v>
+      </c>
+      <c r="G4" t="s">
+        <v>40</v>
       </c>
       <c r="H4">
-        <v>54.76</v>
+        <v>1.49</v>
       </c>
       <c r="I4" s="1">
-        <v>1.51</v>
+        <v>28.31</v>
       </c>
       <c r="J4">
-        <v>55.87</v>
-      </c>
-      <c r="K4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+        <v>1.52</v>
+      </c>
+      <c r="K4" s="1">
+        <v>28.88</v>
+      </c>
+      <c r="L4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46195</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F5">
-        <v>40.39</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1.48</v>
+        <v>53</v>
+      </c>
+      <c r="G5" t="s">
+        <v>40</v>
       </c>
       <c r="H5">
-        <v>59.78</v>
+        <v>1.49</v>
       </c>
       <c r="I5" s="1">
-        <v>1.51</v>
+        <v>78.97</v>
       </c>
       <c r="J5">
-        <v>60.99</v>
-      </c>
-      <c r="K5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>1.52</v>
+      </c>
+      <c r="K5" s="1">
+        <v>80.56</v>
+      </c>
+      <c r="L5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M5">
+        <v>54300</v>
+      </c>
+      <c r="N5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
         <v>46195</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F6">
-        <v>53</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1.49</v>
+        <v>40.39</v>
+      </c>
+      <c r="G6" t="s">
+        <v>40</v>
       </c>
       <c r="H6">
-        <v>78.97</v>
+        <v>1.48</v>
       </c>
       <c r="I6" s="1">
-        <v>1.52</v>
+        <v>59.78</v>
       </c>
       <c r="J6">
-        <v>80.56</v>
-      </c>
-      <c r="K6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+        <v>1.51</v>
+      </c>
+      <c r="K6" s="1">
+        <v>60.99</v>
+      </c>
+      <c r="L6" t="s">
+        <v>44</v>
+      </c>
+      <c r="M6">
+        <v>3722</v>
+      </c>
+      <c r="N6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="3">
         <v>46195</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F7">
-        <v>19</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1.49</v>
+        <v>37</v>
+      </c>
+      <c r="G7" t="s">
+        <v>40</v>
       </c>
       <c r="H7">
-        <v>28.31</v>
+        <v>1.48</v>
       </c>
       <c r="I7" s="1">
-        <v>1.52</v>
+        <v>54.76</v>
       </c>
       <c r="J7">
-        <v>28.88</v>
-      </c>
-      <c r="K7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+        <v>1.51</v>
+      </c>
+      <c r="K7" s="1">
+        <v>55.87</v>
+      </c>
+      <c r="L7" t="s">
+        <v>45</v>
+      </c>
+      <c r="M7">
+        <v>3098</v>
+      </c>
+      <c r="N7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="3">
         <v>46197</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
         <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F8">
         <v>15</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8">
         <v>1.48</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>22.2</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.51</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>22.65</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
+        <v>46</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9">
+        <v>20</v>
+      </c>
+      <c r="G9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9">
+        <v>1.48</v>
+      </c>
+      <c r="I9" s="1">
+        <v>29.6</v>
+      </c>
+      <c r="J9">
+        <v>1.51</v>
+      </c>
+      <c r="K9" s="1">
+        <v>30.2</v>
+      </c>
+      <c r="L9" t="s">
+        <v>47</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10">
+        <v>1.48</v>
+      </c>
+      <c r="I10" s="1">
+        <v>22.2</v>
+      </c>
+      <c r="J10">
+        <v>1.51</v>
+      </c>
+      <c r="K10" s="1">
+        <v>22.65</v>
+      </c>
+      <c r="L10" t="s">
+        <v>48</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="4" t="s">
+      <c r="E11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11">
+        <v>36.9</v>
+      </c>
+      <c r="G11" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11">
+        <v>1.47</v>
+      </c>
+      <c r="I11" s="1">
+        <v>54.24</v>
+      </c>
+      <c r="J11">
+        <v>1.5</v>
+      </c>
+      <c r="K11" s="1">
+        <v>55.35</v>
+      </c>
+      <c r="L11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M11">
+        <v>4021</v>
+      </c>
+      <c r="N11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="5" t="s">
+      <c r="E12" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12">
+        <v>5</v>
+      </c>
+      <c r="G12" t="s">
+        <v>40</v>
+      </c>
+      <c r="H12">
+        <v>1.47</v>
+      </c>
+      <c r="I12" s="1">
+        <v>7.35</v>
+      </c>
+      <c r="J12">
+        <v>1.5</v>
+      </c>
+      <c r="K12" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="L12" t="s">
+        <v>50</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13">
+        <v>15</v>
+      </c>
+      <c r="G13" t="s">
+        <v>40</v>
+      </c>
+      <c r="H13">
+        <v>1.48</v>
+      </c>
+      <c r="I13" s="1">
+        <v>22.2</v>
+      </c>
+      <c r="J13">
+        <v>1.51</v>
+      </c>
+      <c r="K13" s="1">
+        <v>22.65</v>
+      </c>
+      <c r="L13" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14">
+        <v>21</v>
+      </c>
+      <c r="G14" t="s">
+        <v>40</v>
+      </c>
+      <c r="H14">
+        <v>1.47</v>
+      </c>
+      <c r="I14" s="1">
+        <v>30.87</v>
+      </c>
+      <c r="J14">
+        <v>1.5</v>
+      </c>
+      <c r="K14" s="1">
+        <v>31.5</v>
+      </c>
+      <c r="L14" t="s">
+        <v>51</v>
+      </c>
+      <c r="M14">
+        <v>3380</v>
+      </c>
+      <c r="N14" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15">
+        <v>36.21</v>
+      </c>
+      <c r="G15" t="s">
+        <v>40</v>
+      </c>
+      <c r="H15">
+        <v>1.47</v>
+      </c>
+      <c r="I15" s="1">
+        <v>53.23</v>
+      </c>
+      <c r="J15">
+        <v>1.5</v>
+      </c>
+      <c r="K15" s="1">
+        <v>54.32</v>
+      </c>
+      <c r="L15" t="s">
+        <v>52</v>
+      </c>
+      <c r="M15">
+        <v>3996</v>
+      </c>
+      <c r="N15" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="E16" t="s">
+        <v>39</v>
+      </c>
+      <c r="F16">
+        <v>8</v>
+      </c>
+      <c r="G16" t="s">
+        <v>40</v>
+      </c>
+      <c r="H16">
+        <v>1.47</v>
+      </c>
+      <c r="I16" s="1">
+        <v>11.76</v>
+      </c>
+      <c r="J16">
+        <v>1.5</v>
+      </c>
+      <c r="K16" s="1">
+        <v>12</v>
+      </c>
+      <c r="L16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M16">
+        <v>242919</v>
+      </c>
+      <c r="N16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="F17">
+        <v>25.01</v>
+      </c>
+      <c r="G17" t="s">
+        <v>40</v>
+      </c>
+      <c r="H17">
+        <v>1.48</v>
+      </c>
+      <c r="I17" s="1">
+        <v>37.01</v>
+      </c>
+      <c r="J17">
+        <v>1.51</v>
+      </c>
+      <c r="K17" s="1">
+        <v>37.77</v>
+      </c>
+      <c r="L17" t="s">
+        <v>54</v>
+      </c>
+      <c r="M17">
+        <v>54500</v>
+      </c>
+      <c r="N17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" s="5" t="s">
+      <c r="F18">
+        <v>11.84</v>
+      </c>
+      <c r="G18" t="s">
+        <v>40</v>
+      </c>
+      <c r="H18">
+        <v>1.47</v>
+      </c>
+      <c r="I18" s="1">
+        <v>17.4</v>
+      </c>
+      <c r="J18">
+        <v>1.5</v>
+      </c>
+      <c r="K18" s="1">
+        <v>17.76</v>
+      </c>
+      <c r="L18" t="s">
+        <v>55</v>
+      </c>
+      <c r="M18">
+        <v>4160</v>
+      </c>
+      <c r="N18" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="7">
+        <v>201.51</v>
+      </c>
+      <c r="C23" s="7">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="7">
-        <v>99.23</v>
-      </c>
-      <c r="C13" s="7">
-        <v>4</v>
-      </c>
-      <c r="D13" s="8">
-        <v>1.4934</v>
-      </c>
-      <c r="E13" s="7">
-        <v>148.19</v>
-      </c>
-      <c r="F13" s="7">
-        <v>151.17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="7">
-        <v>82.56</v>
-      </c>
-      <c r="C14" s="7">
-        <v>3</v>
-      </c>
-      <c r="D14" s="8">
-        <v>1.482</v>
-      </c>
-      <c r="E14" s="7">
-        <v>122.35</v>
-      </c>
-      <c r="F14" s="7">
-        <v>124.82</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="10">
-        <v>181.79</v>
-      </c>
-      <c r="C15" s="10">
-        <v>7</v>
-      </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="10">
-        <v>270.54</v>
-      </c>
-      <c r="F15" s="10">
-        <v>275.99</v>
+      <c r="D23" s="8">
+        <v>1.4749</v>
+      </c>
+      <c r="E23" s="7">
+        <v>297.2</v>
+      </c>
+      <c r="F23" s="7">
+        <v>303.25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="7">
+        <v>174.24</v>
+      </c>
+      <c r="C24" s="7">
+        <v>8</v>
+      </c>
+      <c r="D24" s="8">
+        <v>1.4876</v>
+      </c>
+      <c r="E24" s="7">
+        <v>259.2</v>
+      </c>
+      <c r="F24" s="7">
+        <v>264.44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" s="10">
+        <v>375.75</v>
+      </c>
+      <c r="C25" s="10">
+        <v>17</v>
+      </c>
+      <c r="D25" s="8"/>
+      <c r="E25" s="10">
+        <v>556.4</v>
+      </c>
+      <c r="F25" s="10">
+        <v>567.6900000000001</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="60">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,16 +55,16 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1146 Варна Сливница</t>
-  </si>
-  <si>
-    <t>1147 Варна Ситроен</t>
-  </si>
-  <si>
-    <t>1158 Варна Чайка</t>
-  </si>
-  <si>
-    <t>1199 Varna Car Osvoboditel</t>
+    <t>Варна Сливница</t>
+  </si>
+  <si>
+    <t>Варна</t>
+  </si>
+  <si>
+    <t>Варна Чайка</t>
+  </si>
+  <si>
+    <t>Варна Варненчик</t>
   </si>
   <si>
     <t>ТубаДДД5</t>
@@ -76,27 +73,27 @@
     <t>ТубаДДД1</t>
   </si>
   <si>
+    <t>В4601ХК</t>
+  </si>
+  <si>
+    <t>В4602ХК</t>
+  </si>
+  <si>
+    <t>В8262ВР</t>
+  </si>
+  <si>
     <t>ТубаДДД6</t>
   </si>
   <si>
-    <t>В8262ВР</t>
-  </si>
-  <si>
-    <t>В4602ХК</t>
-  </si>
-  <si>
-    <t>В4601ХК</t>
-  </si>
-  <si>
     <t>ТубаДДД4</t>
   </si>
   <si>
+    <t>ТубаДДД3</t>
+  </si>
+  <si>
     <t>В4603ХК</t>
   </si>
   <si>
-    <t>ТубаДДД3</t>
-  </si>
-  <si>
     <t>В2658НА</t>
   </si>
   <si>
@@ -106,27 +103,27 @@
     <t>78970155027720436</t>
   </si>
   <si>
+    <t>78970155027720386</t>
+  </si>
+  <si>
+    <t>78970155027720394</t>
+  </si>
+  <si>
+    <t>78970155027720428</t>
+  </si>
+  <si>
     <t>78970155027720485</t>
   </si>
   <si>
-    <t>78970155027720428</t>
-  </si>
-  <si>
-    <t>78970155027720394</t>
-  </si>
-  <si>
-    <t>78970155027720386</t>
-  </si>
-  <si>
     <t>78970155027720469</t>
   </si>
   <si>
+    <t>78970155027720451</t>
+  </si>
+  <si>
     <t>78970155027720402</t>
   </si>
   <si>
-    <t>78970155027720451</t>
-  </si>
-  <si>
     <t>78970155027720410</t>
   </si>
   <si>
@@ -136,103 +133,49 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>10:59:00</t>
-  </si>
-  <si>
-    <t>13:41:00</t>
-  </si>
-  <si>
-    <t>13:39:00</t>
-  </si>
-  <si>
-    <t>11:36:00</t>
-  </si>
-  <si>
-    <t>10:28:00</t>
-  </si>
-  <si>
-    <t>11:02:00</t>
-  </si>
-  <si>
-    <t>05:47:00</t>
-  </si>
-  <si>
-    <t>07:06:00</t>
-  </si>
-  <si>
-    <t>06:05:00</t>
-  </si>
-  <si>
-    <t>06:04:00</t>
-  </si>
-  <si>
-    <t>17:35:00</t>
-  </si>
-  <si>
-    <t>11:06:00</t>
-  </si>
-  <si>
-    <t>14:04:00</t>
-  </si>
-  <si>
-    <t>09:02:00</t>
-  </si>
-  <si>
-    <t>12:52:00</t>
-  </si>
-  <si>
-    <t>3233569167 3233569167</t>
-  </si>
-  <si>
-    <t>3233569168 3233569168</t>
-  </si>
-  <si>
-    <t>3233717171 3233717171</t>
-  </si>
-  <si>
-    <t>3233717942 3233717942</t>
-  </si>
-  <si>
-    <t>3233720228 3233720228</t>
-  </si>
-  <si>
-    <t>3233726352 3233726352</t>
-  </si>
-  <si>
-    <t>3233809271 3233809271</t>
-  </si>
-  <si>
-    <t>3233877529 3233877529</t>
-  </si>
-  <si>
-    <t>3234037053 3234037053</t>
-  </si>
-  <si>
-    <t>3234029542 3234029542</t>
-  </si>
-  <si>
-    <t>3234045264 3234045264</t>
-  </si>
-  <si>
-    <t>3234046101 3234046101</t>
-  </si>
-  <si>
-    <t>3234109358 3234109358</t>
-  </si>
-  <si>
-    <t>3234101045 3234101045</t>
-  </si>
-  <si>
-    <t>3234108455 3234108455</t>
-  </si>
-  <si>
-    <t>3234104146 3234104146</t>
-  </si>
-  <si>
-    <t>3234114612 3234114612</t>
+    <t>10:59</t>
+  </si>
+  <si>
+    <t>10:28</t>
+  </si>
+  <si>
+    <t>11:36</t>
+  </si>
+  <si>
+    <t>13:39</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>11:04</t>
+  </si>
+  <si>
+    <t>05:47</t>
+  </si>
+  <si>
+    <t>06:04</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>07:05</t>
+  </si>
+  <si>
+    <t>09:04</t>
+  </si>
+  <si>
+    <t>11:06</t>
+  </si>
+  <si>
+    <t>12:55</t>
+  </si>
+  <si>
+    <t>14:04</t>
+  </si>
+  <si>
+    <t>17:35</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ</t>
@@ -652,7 +595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -661,17 +604,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -711,143 +653,131 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46192</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2">
         <v>12.23</v>
       </c>
-      <c r="G2" t="s">
-        <v>40</v>
+      <c r="G2" s="1">
+        <v>1.53</v>
       </c>
       <c r="H2">
-        <v>1.53</v>
+        <v>18.71</v>
       </c>
       <c r="I2" s="1">
-        <v>18.71</v>
+        <v>1.56</v>
       </c>
       <c r="J2">
-        <v>1.56</v>
-      </c>
-      <c r="K2" s="1">
         <v>19.08</v>
       </c>
-      <c r="L2" t="s">
-        <v>41</v>
+      <c r="K2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>143743</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46192</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F3">
         <v>5.17</v>
       </c>
-      <c r="G3" t="s">
-        <v>40</v>
+      <c r="G3" s="1">
+        <v>1.51</v>
       </c>
       <c r="H3">
-        <v>1.51</v>
+        <v>7.81</v>
       </c>
       <c r="I3" s="1">
-        <v>7.81</v>
+        <v>1.54</v>
       </c>
       <c r="J3">
-        <v>1.54</v>
-      </c>
-      <c r="K3" s="1">
         <v>7.96</v>
       </c>
-      <c r="L3" t="s">
-        <v>41</v>
+      <c r="K3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>143744</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46195</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
         <v>38</v>
       </c>
       <c r="F4">
-        <v>19</v>
-      </c>
-      <c r="G4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.48</v>
+      </c>
+      <c r="H4">
+        <v>54.76</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="J4">
+        <v>55.87</v>
+      </c>
+      <c r="K4" t="s">
         <v>40</v>
       </c>
-      <c r="H4">
-        <v>1.49</v>
-      </c>
-      <c r="I4" s="1">
-        <v>28.31</v>
-      </c>
-      <c r="J4">
-        <v>1.52</v>
-      </c>
-      <c r="K4" s="1">
-        <v>28.88</v>
-      </c>
-      <c r="L4" t="s">
-        <v>42</v>
+      <c r="L4">
+        <v>3098</v>
       </c>
       <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>277336</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
         <v>46195</v>
       </c>
@@ -855,43 +785,40 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
         <v>38</v>
       </c>
       <c r="F5">
-        <v>53</v>
-      </c>
-      <c r="G5" t="s">
-        <v>40</v>
+        <v>40.39</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1.48</v>
       </c>
       <c r="H5">
-        <v>1.49</v>
+        <v>59.78</v>
       </c>
       <c r="I5" s="1">
-        <v>78.97</v>
+        <v>1.51</v>
       </c>
       <c r="J5">
-        <v>1.52</v>
-      </c>
-      <c r="K5" s="1">
-        <v>80.56</v>
-      </c>
-      <c r="L5" t="s">
-        <v>43</v>
+        <v>60.99</v>
+      </c>
+      <c r="K5" t="s">
+        <v>41</v>
+      </c>
+      <c r="L5">
+        <v>3722</v>
       </c>
       <c r="M5">
-        <v>54300</v>
-      </c>
-      <c r="N5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>117000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="3">
         <v>46195</v>
       </c>
@@ -899,573 +826,534 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F6">
-        <v>40.39</v>
-      </c>
-      <c r="G6" t="s">
-        <v>40</v>
+        <v>53</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1.49</v>
       </c>
       <c r="H6">
-        <v>1.48</v>
+        <v>78.97</v>
       </c>
       <c r="I6" s="1">
-        <v>59.78</v>
+        <v>1.52</v>
       </c>
       <c r="J6">
-        <v>1.51</v>
-      </c>
-      <c r="K6" s="1">
-        <v>60.99</v>
-      </c>
-      <c r="L6" t="s">
-        <v>44</v>
+        <v>80.56</v>
+      </c>
+      <c r="K6" t="s">
+        <v>42</v>
+      </c>
+      <c r="L6">
+        <v>54300</v>
       </c>
       <c r="M6">
-        <v>3722</v>
-      </c>
-      <c r="N6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>117811</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="3">
         <v>46195</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F7">
-        <v>37</v>
-      </c>
-      <c r="G7" t="s">
-        <v>40</v>
+        <v>19</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1.49</v>
       </c>
       <c r="H7">
-        <v>1.48</v>
+        <v>28.31</v>
       </c>
       <c r="I7" s="1">
-        <v>54.76</v>
+        <v>1.52</v>
       </c>
       <c r="J7">
-        <v>1.51</v>
-      </c>
-      <c r="K7" s="1">
-        <v>55.87</v>
-      </c>
-      <c r="L7" t="s">
-        <v>45</v>
+        <v>28.88</v>
+      </c>
+      <c r="K7" t="s">
+        <v>43</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
       </c>
       <c r="M7">
-        <v>3098</v>
-      </c>
-      <c r="N7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>117814</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="3">
         <v>46197</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F8">
         <v>15</v>
       </c>
-      <c r="G8" t="s">
-        <v>40</v>
+      <c r="G8" s="1">
+        <v>1.48</v>
       </c>
       <c r="H8">
-        <v>1.48</v>
+        <v>22.2</v>
       </c>
       <c r="I8" s="1">
-        <v>22.2</v>
+        <v>1.51</v>
       </c>
       <c r="J8">
-        <v>1.51</v>
-      </c>
-      <c r="K8" s="1">
         <v>22.65</v>
       </c>
-      <c r="L8" t="s">
-        <v>46</v>
+      <c r="K8" t="s">
+        <v>44</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
       </c>
       <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+        <v>277931</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="3">
         <v>46199</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F9">
         <v>20</v>
       </c>
-      <c r="G9" t="s">
-        <v>40</v>
+      <c r="G9" s="1">
+        <v>1.48</v>
       </c>
       <c r="H9">
-        <v>1.48</v>
+        <v>29.6</v>
       </c>
       <c r="I9" s="1">
-        <v>29.6</v>
+        <v>1.51</v>
       </c>
       <c r="J9">
-        <v>1.51</v>
-      </c>
-      <c r="K9" s="1">
         <v>30.2</v>
       </c>
-      <c r="L9" t="s">
-        <v>47</v>
+      <c r="K9" t="s">
+        <v>45</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
       </c>
       <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>49527</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="3">
         <v>46202</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F10">
         <v>15</v>
       </c>
-      <c r="G10" t="s">
-        <v>40</v>
+      <c r="G10" s="1">
+        <v>1.48</v>
       </c>
       <c r="H10">
-        <v>1.48</v>
+        <v>22.2</v>
       </c>
       <c r="I10" s="1">
-        <v>22.2</v>
+        <v>1.51</v>
       </c>
       <c r="J10">
-        <v>1.51</v>
-      </c>
-      <c r="K10" s="1">
         <v>22.65</v>
       </c>
-      <c r="L10" t="s">
-        <v>48</v>
+      <c r="K10" t="s">
+        <v>46</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
       </c>
       <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>207327</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="3">
         <v>46202</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F11">
-        <v>36.9</v>
-      </c>
-      <c r="G11" t="s">
-        <v>40</v>
+        <v>5</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1.47</v>
       </c>
       <c r="H11">
-        <v>1.47</v>
+        <v>7.35</v>
       </c>
       <c r="I11" s="1">
-        <v>54.24</v>
+        <v>1.5</v>
       </c>
       <c r="J11">
-        <v>1.5</v>
-      </c>
-      <c r="K11" s="1">
-        <v>55.35</v>
-      </c>
-      <c r="L11" t="s">
-        <v>49</v>
+        <v>7.5</v>
+      </c>
+      <c r="K11" t="s">
+        <v>46</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
       </c>
       <c r="M11">
-        <v>4021</v>
-      </c>
-      <c r="N11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>207328</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="3">
         <v>46202</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F12">
-        <v>5</v>
-      </c>
-      <c r="G12" t="s">
-        <v>40</v>
+        <v>36.9</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1.47</v>
       </c>
       <c r="H12">
-        <v>1.47</v>
+        <v>54.24</v>
       </c>
       <c r="I12" s="1">
-        <v>7.35</v>
+        <v>1.5</v>
       </c>
       <c r="J12">
-        <v>1.5</v>
-      </c>
-      <c r="K12" s="1">
-        <v>7.5</v>
-      </c>
-      <c r="L12" t="s">
-        <v>50</v>
+        <v>55.35</v>
+      </c>
+      <c r="K12" t="s">
+        <v>47</v>
+      </c>
+      <c r="L12">
+        <v>4021</v>
       </c>
       <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+        <v>207329</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="3">
         <v>46202</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F13">
         <v>15</v>
       </c>
-      <c r="G13" t="s">
-        <v>40</v>
+      <c r="G13" s="1">
+        <v>1.48</v>
       </c>
       <c r="H13">
-        <v>1.48</v>
+        <v>22.2</v>
       </c>
       <c r="I13" s="1">
-        <v>22.2</v>
+        <v>1.51</v>
       </c>
       <c r="J13">
-        <v>1.51</v>
-      </c>
-      <c r="K13" s="1">
         <v>22.65</v>
       </c>
-      <c r="L13" t="s">
-        <v>50</v>
+      <c r="K13" t="s">
+        <v>48</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
       </c>
       <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+        <v>146242</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="3">
         <v>46203</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E14" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F14">
-        <v>21</v>
-      </c>
-      <c r="G14" t="s">
-        <v>40</v>
+        <v>25.01</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1.48</v>
       </c>
       <c r="H14">
-        <v>1.47</v>
+        <v>37.01</v>
       </c>
       <c r="I14" s="1">
-        <v>30.87</v>
+        <v>1.51</v>
       </c>
       <c r="J14">
-        <v>1.5</v>
-      </c>
-      <c r="K14" s="1">
-        <v>31.5</v>
-      </c>
-      <c r="L14" t="s">
-        <v>51</v>
+        <v>37.77</v>
+      </c>
+      <c r="K14" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14">
+        <v>54500</v>
       </c>
       <c r="M14">
-        <v>3380</v>
-      </c>
-      <c r="N14" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+        <v>279501</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="3">
         <v>46203</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F15">
         <v>36.21</v>
       </c>
-      <c r="G15" t="s">
-        <v>40</v>
+      <c r="G15" s="1">
+        <v>1.47</v>
       </c>
       <c r="H15">
-        <v>1.47</v>
+        <v>53.23</v>
       </c>
       <c r="I15" s="1">
-        <v>53.23</v>
+        <v>1.5</v>
       </c>
       <c r="J15">
-        <v>1.5</v>
-      </c>
-      <c r="K15" s="1">
         <v>54.32</v>
       </c>
-      <c r="L15" t="s">
-        <v>52</v>
+      <c r="K15" t="s">
+        <v>50</v>
+      </c>
+      <c r="L15">
+        <v>3996</v>
       </c>
       <c r="M15">
-        <v>3996</v>
-      </c>
-      <c r="N15" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+        <v>121515</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="3">
         <v>46203</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F16">
-        <v>8</v>
-      </c>
-      <c r="G16" t="s">
-        <v>40</v>
+        <v>11.84</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1.47</v>
       </c>
       <c r="H16">
-        <v>1.47</v>
+        <v>17.4</v>
       </c>
       <c r="I16" s="1">
-        <v>11.76</v>
+        <v>1.5</v>
       </c>
       <c r="J16">
-        <v>1.5</v>
-      </c>
-      <c r="K16" s="1">
-        <v>12</v>
-      </c>
-      <c r="L16" t="s">
-        <v>53</v>
+        <v>17.76</v>
+      </c>
+      <c r="K16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L16">
+        <v>4160</v>
       </c>
       <c r="M16">
-        <v>242919</v>
-      </c>
-      <c r="N16" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+        <v>279582</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="3">
         <v>46203</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E17" t="s">
         <v>38</v>
       </c>
       <c r="F17">
-        <v>25.01</v>
-      </c>
-      <c r="G17" t="s">
-        <v>40</v>
+        <v>8</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1.47</v>
       </c>
       <c r="H17">
-        <v>1.48</v>
+        <v>11.76</v>
       </c>
       <c r="I17" s="1">
-        <v>37.01</v>
+        <v>1.5</v>
       </c>
       <c r="J17">
-        <v>1.51</v>
-      </c>
-      <c r="K17" s="1">
-        <v>37.77</v>
-      </c>
-      <c r="L17" t="s">
-        <v>54</v>
+        <v>12</v>
+      </c>
+      <c r="K17" t="s">
+        <v>52</v>
+      </c>
+      <c r="L17">
+        <v>242919</v>
       </c>
       <c r="M17">
-        <v>54500</v>
-      </c>
-      <c r="N17" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+        <v>121623</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="3">
         <v>46203</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D18" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F18">
-        <v>11.84</v>
-      </c>
-      <c r="G18" t="s">
-        <v>40</v>
+        <v>21</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1.47</v>
       </c>
       <c r="H18">
-        <v>1.47</v>
+        <v>30.87</v>
       </c>
       <c r="I18" s="1">
-        <v>17.4</v>
+        <v>1.5</v>
       </c>
       <c r="J18">
-        <v>1.5</v>
-      </c>
-      <c r="K18" s="1">
-        <v>17.76</v>
-      </c>
-      <c r="L18" t="s">
-        <v>55</v>
+        <v>31.5</v>
+      </c>
+      <c r="K18" t="s">
+        <v>53</v>
+      </c>
+      <c r="L18">
+        <v>3380</v>
       </c>
       <c r="M18">
-        <v>4160</v>
-      </c>
-      <c r="N18" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
+        <v>208474</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="4" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -1473,29 +1361,29 @@
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:13">
       <c r="A22" s="5" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23" s="7">
         <v>201.51</v>
@@ -1513,9 +1401,9 @@
         <v>303.25</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:13">
       <c r="A24" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B24" s="7">
         <v>174.24</v>
@@ -1533,9 +1421,9 @@
         <v>264.44</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:13">
       <c r="A25" s="9" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="B25" s="10">
         <v>375.75</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="74">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,6 +55,9 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-07</t>
   </si>
   <si>
@@ -61,13 +67,34 @@
     <t>2026-07-13</t>
   </si>
   <si>
-    <t>Варна Порт</t>
-  </si>
-  <si>
-    <t>Варна Сливница</t>
-  </si>
-  <si>
-    <t>Варна</t>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
   </si>
   <si>
     <t>ТубаДДД4</t>
@@ -79,6 +106,15 @@
     <t>В4601ХК</t>
   </si>
   <si>
+    <t>В4603ХК</t>
+  </si>
+  <si>
+    <t>В8262ВР</t>
+  </si>
+  <si>
+    <t>В2658НА</t>
+  </si>
+  <si>
     <t>78970155027720469</t>
   </si>
   <si>
@@ -88,19 +124,100 @@
     <t>78970155027720386</t>
   </si>
   <si>
+    <t>78970155027720402</t>
+  </si>
+  <si>
+    <t>78970155027720428</t>
+  </si>
+  <si>
+    <t>78970155027720410</t>
+  </si>
+  <si>
     <t>DIESEL DOUBLE FILTERED</t>
   </si>
   <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>2026-07-07 06:37:56</t>
-  </si>
-  <si>
-    <t>2026-07-09 12:01:50</t>
-  </si>
-  <si>
-    <t>2026-07-13 12:57:35</t>
+    <t>DIESEL EKONOMY</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>06:37:00</t>
+  </si>
+  <si>
+    <t>12:02:00</t>
+  </si>
+  <si>
+    <t>12:58:00</t>
+  </si>
+  <si>
+    <t>12:48:00</t>
+  </si>
+  <si>
+    <t>08:15:00</t>
+  </si>
+  <si>
+    <t>07:28:00</t>
+  </si>
+  <si>
+    <t>12:40:00</t>
+  </si>
+  <si>
+    <t>08:47:00</t>
+  </si>
+  <si>
+    <t>11:28:00</t>
+  </si>
+  <si>
+    <t>11:57:00</t>
+  </si>
+  <si>
+    <t>14:32:00</t>
+  </si>
+  <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
+    <t>3234438871 3234438871</t>
+  </si>
+  <si>
+    <t>3234522658 3234522658</t>
+  </si>
+  <si>
+    <t>3234750994 3234750994</t>
+  </si>
+  <si>
+    <t>3234957125 3234957125</t>
+  </si>
+  <si>
+    <t>3235171427 3235171427</t>
+  </si>
+  <si>
+    <t>3235166032 3235166032</t>
+  </si>
+  <si>
+    <t>3235441853 3235441853</t>
+  </si>
+  <si>
+    <t>3235582771 3235582771</t>
+  </si>
+  <si>
+    <t>3235620617 3235620617</t>
+  </si>
+  <si>
+    <t>3235620966 3235620966</t>
+  </si>
+  <si>
+    <t>3235629738 3235629738</t>
+  </si>
+  <si>
+    <t>3235635425 3235635425</t>
+  </si>
+  <si>
+    <t>3235647235 3235647235</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ</t>
@@ -518,7 +635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -527,15 +644,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -572,212 +691,696 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F2">
         <v>20</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2">
         <v>1.75</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>35</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.78</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>35.6</v>
       </c>
-      <c r="K2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2">
+      <c r="L2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="N2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F3">
         <v>40</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3">
         <v>1.46</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>58.4</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.49</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>59.6</v>
       </c>
-      <c r="K3" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3">
+      <c r="L3" t="s">
+        <v>44</v>
+      </c>
+      <c r="M3">
         <v>4284</v>
       </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="N3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F4">
         <v>38.85</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4">
         <v>1.46</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>56.72</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.49</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>57.89</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>45</v>
+      </c>
+      <c r="M4">
+        <v>3787</v>
+      </c>
+      <c r="N4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5">
+        <v>41.68</v>
+      </c>
+      <c r="G5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5">
+        <v>1.48</v>
+      </c>
+      <c r="I5" s="1">
+        <v>61.69</v>
+      </c>
+      <c r="J5">
+        <v>1.51</v>
+      </c>
+      <c r="K5" s="1">
+        <v>62.94</v>
+      </c>
+      <c r="L5" t="s">
+        <v>46</v>
+      </c>
+      <c r="M5">
+        <v>4498</v>
+      </c>
+      <c r="N5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
         <v>28</v>
       </c>
-      <c r="L4">
-        <v>3787</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="3" t="s">
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6">
+        <v>35.75</v>
+      </c>
+      <c r="G6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6">
+        <v>1.51</v>
+      </c>
+      <c r="I6" s="1">
+        <v>53.98</v>
+      </c>
+      <c r="J6">
+        <v>1.54</v>
+      </c>
+      <c r="K6" s="1">
+        <v>55.06</v>
+      </c>
+      <c r="L6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6">
+        <v>4570</v>
+      </c>
+      <c r="N6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7">
+        <v>55.32</v>
+      </c>
+      <c r="G7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7">
+        <v>1.65</v>
+      </c>
+      <c r="I7" s="1">
+        <v>91.28</v>
+      </c>
+      <c r="J7">
+        <v>1.68</v>
+      </c>
+      <c r="K7" s="1">
+        <v>92.94</v>
+      </c>
+      <c r="L7" t="s">
+        <v>48</v>
+      </c>
+      <c r="M7">
+        <v>54964</v>
+      </c>
+      <c r="N7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8">
+        <v>27.48</v>
+      </c>
+      <c r="G8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8">
+        <v>1.53</v>
+      </c>
+      <c r="I8" s="1">
+        <v>42.04</v>
+      </c>
+      <c r="J8">
+        <v>1.56</v>
+      </c>
+      <c r="K8" s="1">
+        <v>42.87</v>
+      </c>
+      <c r="L8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M8">
+        <v>4780</v>
+      </c>
+      <c r="N8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="4" t="s">
+      <c r="D9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9">
+        <v>10</v>
+      </c>
+      <c r="G9" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9">
+        <v>1.52</v>
+      </c>
+      <c r="I9" s="1">
+        <v>15.2</v>
+      </c>
+      <c r="J9">
+        <v>1.55</v>
+      </c>
+      <c r="K9" s="1">
+        <v>15.5</v>
+      </c>
+      <c r="L9" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9">
+        <v>4100</v>
+      </c>
+      <c r="N9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10">
+        <v>24.81</v>
+      </c>
+      <c r="G10" t="s">
+        <v>42</v>
+      </c>
+      <c r="H10">
+        <v>1.52</v>
+      </c>
+      <c r="I10" s="1">
+        <v>37.71</v>
+      </c>
+      <c r="J10">
+        <v>1.55</v>
+      </c>
+      <c r="K10" s="1">
+        <v>38.46</v>
+      </c>
+      <c r="L10" t="s">
+        <v>46</v>
+      </c>
+      <c r="M10">
+        <v>243034</v>
+      </c>
+      <c r="N10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11">
+        <v>21.84</v>
+      </c>
+      <c r="G11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H11">
+        <v>1.74</v>
+      </c>
+      <c r="I11" s="1">
+        <v>38</v>
+      </c>
+      <c r="J11">
+        <v>1.77</v>
+      </c>
+      <c r="K11" s="1">
+        <v>38.66</v>
+      </c>
+      <c r="L11" t="s">
+        <v>51</v>
+      </c>
+      <c r="M11">
+        <v>55100</v>
+      </c>
+      <c r="N11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12">
+        <v>33.3</v>
+      </c>
+      <c r="G12" t="s">
+        <v>42</v>
+      </c>
+      <c r="H12">
+        <v>1.52</v>
+      </c>
+      <c r="I12" s="1">
+        <v>50.62</v>
+      </c>
+      <c r="J12">
+        <v>1.55</v>
+      </c>
+      <c r="K12" s="1">
+        <v>51.61</v>
+      </c>
+      <c r="L12" t="s">
+        <v>52</v>
+      </c>
+      <c r="M12">
+        <v>4163</v>
+      </c>
+      <c r="N12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="5" t="s">
+      <c r="D13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13">
+        <v>16.57</v>
+      </c>
+      <c r="G13" t="s">
+        <v>42</v>
+      </c>
+      <c r="H13">
+        <v>1.52</v>
+      </c>
+      <c r="I13" s="1">
+        <v>25.19</v>
+      </c>
+      <c r="J13">
+        <v>1.55</v>
+      </c>
+      <c r="K13" s="1">
+        <v>25.68</v>
+      </c>
+      <c r="L13" t="s">
+        <v>53</v>
+      </c>
+      <c r="M13">
+        <v>4953</v>
+      </c>
+      <c r="N13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="6">
-        <v>78.84999999999999</v>
-      </c>
-      <c r="C9" s="6">
+      <c r="C14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14">
+        <v>30.69</v>
+      </c>
+      <c r="G14" t="s">
+        <v>42</v>
+      </c>
+      <c r="H14">
+        <v>1.52</v>
+      </c>
+      <c r="I14" s="1">
+        <v>46.65</v>
+      </c>
+      <c r="J14">
+        <v>1.55</v>
+      </c>
+      <c r="K14" s="1">
+        <v>47.57</v>
+      </c>
+      <c r="L14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M14">
+        <v>4840</v>
+      </c>
+      <c r="N14" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="6">
+        <v>299.13</v>
+      </c>
+      <c r="C19" s="6">
+        <v>10</v>
+      </c>
+      <c r="D19" s="7">
+        <v>1.4983</v>
+      </c>
+      <c r="E19" s="6">
+        <v>448.2</v>
+      </c>
+      <c r="F19" s="6">
+        <v>457.18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="6">
+        <v>77.16</v>
+      </c>
+      <c r="C20" s="6">
         <v>2</v>
       </c>
-      <c r="D9" s="7">
-        <v>1.46</v>
-      </c>
-      <c r="E9" s="6">
-        <v>115.12</v>
-      </c>
-      <c r="F9" s="6">
-        <v>117.49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="6">
+      <c r="D20" s="7">
+        <v>1.6755</v>
+      </c>
+      <c r="E20" s="6">
+        <v>129.28</v>
+      </c>
+      <c r="F20" s="6">
+        <v>131.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="6">
         <v>20</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C21" s="6">
         <v>1</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D21" s="7">
         <v>1.75</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E21" s="6">
         <v>35</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F21" s="6">
         <v>35.6</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="9">
-        <v>98.84999999999999</v>
-      </c>
-      <c r="C11" s="9">
-        <v>3</v>
-      </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="9">
-        <v>150.12</v>
-      </c>
-      <c r="F11" s="9">
-        <v>153.09</v>
+    <row r="22" spans="1:6">
+      <c r="A22" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="9">
+        <v>396.29</v>
+      </c>
+      <c r="C22" s="9">
+        <v>13</v>
+      </c>
+      <c r="D22" s="7"/>
+      <c r="E22" s="9">
+        <v>612.48</v>
+      </c>
+      <c r="F22" s="9">
+        <v>624.38</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A17:F17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ.xlsx
@@ -244,7 +244,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -1311,7 +1311,7 @@
         <v>10</v>
       </c>
       <c r="D19" s="7">
-        <v>1.4983</v>
+        <v>1.498345</v>
       </c>
       <c r="E19" s="6">
         <v>448.2</v>
@@ -1331,7 +1331,7 @@
         <v>2</v>
       </c>
       <c r="D20" s="7">
-        <v>1.6755</v>
+        <v>1.67548</v>
       </c>
       <c r="E20" s="6">
         <v>129.28</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="75">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -635,7 +638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -648,13 +651,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -697,582 +700,624 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F2">
         <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H2">
+        <v>1.599</v>
+      </c>
+      <c r="I2" s="1">
         <v>1.75</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>35</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>1.78</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L2" s="1">
         <v>35.6</v>
       </c>
-      <c r="L2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M2">
+      <c r="M2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N2">
         <v>0</v>
       </c>
-      <c r="N2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F3">
         <v>40</v>
       </c>
       <c r="G3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H3">
+        <v>1.359</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.46</v>
+      </c>
+      <c r="J3">
+        <v>58.4</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="L3" s="1">
+        <v>59.6</v>
+      </c>
+      <c r="M3" t="s">
+        <v>45</v>
+      </c>
+      <c r="N3">
+        <v>4284</v>
+      </c>
+      <c r="O3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4">
+        <v>38.852</v>
+      </c>
+      <c r="G4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4">
+        <v>1.359</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.46</v>
+      </c>
+      <c r="J4">
+        <v>56.72392</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="L4" s="1">
+        <v>57.88948</v>
+      </c>
+      <c r="M4" t="s">
+        <v>46</v>
+      </c>
+      <c r="N4">
+        <v>3787</v>
+      </c>
+      <c r="O4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5">
+        <v>41.682</v>
+      </c>
+      <c r="G5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5">
+        <v>1.369</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.48</v>
+      </c>
+      <c r="J5">
+        <v>61.68936</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="L5" s="1">
+        <v>62.93982</v>
+      </c>
+      <c r="M5" t="s">
+        <v>47</v>
+      </c>
+      <c r="N5">
+        <v>4498</v>
+      </c>
+      <c r="O5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6">
+        <v>35.753</v>
+      </c>
+      <c r="G6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6">
+        <v>1.401</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="J6">
+        <v>53.98703</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="L6" s="1">
+        <v>55.05962</v>
+      </c>
+      <c r="M6" t="s">
+        <v>48</v>
+      </c>
+      <c r="N6">
+        <v>4570</v>
+      </c>
+      <c r="O6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
         <v>42</v>
       </c>
-      <c r="H3">
-        <v>1.46</v>
-      </c>
-      <c r="I3" s="1">
-        <v>58.4</v>
-      </c>
-      <c r="J3">
-        <v>1.49</v>
-      </c>
-      <c r="K3" s="1">
-        <v>59.6</v>
-      </c>
-      <c r="L3" t="s">
-        <v>44</v>
-      </c>
-      <c r="M3">
-        <v>4284</v>
-      </c>
-      <c r="N3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F4">
-        <v>38.85</v>
-      </c>
-      <c r="G4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4">
-        <v>1.46</v>
-      </c>
-      <c r="I4" s="1">
-        <v>56.72</v>
-      </c>
-      <c r="J4">
-        <v>1.49</v>
-      </c>
-      <c r="K4" s="1">
-        <v>57.89</v>
-      </c>
-      <c r="L4" t="s">
-        <v>45</v>
-      </c>
-      <c r="M4">
-        <v>3787</v>
-      </c>
-      <c r="N4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="F7">
+        <v>55.321</v>
+      </c>
+      <c r="G7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7">
+        <v>1.588</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1.65</v>
+      </c>
+      <c r="J7">
+        <v>91.27965</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1.68</v>
+      </c>
+      <c r="L7" s="1">
+        <v>92.93928</v>
+      </c>
+      <c r="M7" t="s">
+        <v>49</v>
+      </c>
+      <c r="N7">
+        <v>54964</v>
+      </c>
+      <c r="O7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8">
+        <v>27.481</v>
+      </c>
+      <c r="G8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8">
+        <v>1.401</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="J8">
+        <v>42.04593</v>
+      </c>
+      <c r="K8" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="L8" s="1">
+        <v>42.87036</v>
+      </c>
+      <c r="M8" t="s">
+        <v>50</v>
+      </c>
+      <c r="N8">
+        <v>4780</v>
+      </c>
+      <c r="O8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
         <v>30</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D9" t="s">
         <v>36</v>
       </c>
-      <c r="E5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F5">
-        <v>41.68</v>
-      </c>
-      <c r="G5" t="s">
-        <v>42</v>
-      </c>
-      <c r="H5">
-        <v>1.48</v>
-      </c>
-      <c r="I5" s="1">
-        <v>61.69</v>
-      </c>
-      <c r="J5">
-        <v>1.51</v>
-      </c>
-      <c r="K5" s="1">
-        <v>62.94</v>
-      </c>
-      <c r="L5" t="s">
-        <v>46</v>
-      </c>
-      <c r="M5">
-        <v>4498</v>
-      </c>
-      <c r="N5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6">
-        <v>35.75</v>
-      </c>
-      <c r="G6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6">
-        <v>1.51</v>
-      </c>
-      <c r="I6" s="1">
-        <v>53.98</v>
-      </c>
-      <c r="J6">
-        <v>1.54</v>
-      </c>
-      <c r="K6" s="1">
-        <v>55.06</v>
-      </c>
-      <c r="L6" t="s">
-        <v>47</v>
-      </c>
-      <c r="M6">
-        <v>4570</v>
-      </c>
-      <c r="N6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="E9" t="s">
         <v>41</v>
-      </c>
-      <c r="F7">
-        <v>55.32</v>
-      </c>
-      <c r="G7" t="s">
-        <v>42</v>
-      </c>
-      <c r="H7">
-        <v>1.65</v>
-      </c>
-      <c r="I7" s="1">
-        <v>91.28</v>
-      </c>
-      <c r="J7">
-        <v>1.68</v>
-      </c>
-      <c r="K7" s="1">
-        <v>92.94</v>
-      </c>
-      <c r="L7" t="s">
-        <v>48</v>
-      </c>
-      <c r="M7">
-        <v>54964</v>
-      </c>
-      <c r="N7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8">
-        <v>27.48</v>
-      </c>
-      <c r="G8" t="s">
-        <v>42</v>
-      </c>
-      <c r="H8">
-        <v>1.53</v>
-      </c>
-      <c r="I8" s="1">
-        <v>42.04</v>
-      </c>
-      <c r="J8">
-        <v>1.56</v>
-      </c>
-      <c r="K8" s="1">
-        <v>42.87</v>
-      </c>
-      <c r="L8" t="s">
-        <v>49</v>
-      </c>
-      <c r="M8">
-        <v>4780</v>
-      </c>
-      <c r="N8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" t="s">
-        <v>40</v>
       </c>
       <c r="F9">
         <v>10</v>
       </c>
       <c r="G9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9">
+        <v>1.449</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="J9">
+        <v>15.2</v>
+      </c>
+      <c r="K9" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="L9" s="1">
+        <v>15.5</v>
+      </c>
+      <c r="M9" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9">
+        <v>4100</v>
+      </c>
+      <c r="O9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10">
+        <v>24.813</v>
+      </c>
+      <c r="G10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10">
+        <v>1.459</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="J10">
+        <v>37.71576</v>
+      </c>
+      <c r="K10" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="L10" s="1">
+        <v>38.46015</v>
+      </c>
+      <c r="M10" t="s">
+        <v>47</v>
+      </c>
+      <c r="N10">
+        <v>243034</v>
+      </c>
+      <c r="O10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" t="s">
         <v>42</v>
       </c>
-      <c r="H9">
+      <c r="F11">
+        <v>21.842</v>
+      </c>
+      <c r="G11" t="s">
+        <v>43</v>
+      </c>
+      <c r="H11">
+        <v>1.689</v>
+      </c>
+      <c r="I11" s="1">
+        <v>1.74</v>
+      </c>
+      <c r="J11">
+        <v>38.00508</v>
+      </c>
+      <c r="K11" s="1">
+        <v>1.77</v>
+      </c>
+      <c r="L11" s="1">
+        <v>38.66034</v>
+      </c>
+      <c r="M11" t="s">
+        <v>52</v>
+      </c>
+      <c r="N11">
+        <v>55100</v>
+      </c>
+      <c r="O11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12">
+        <v>33.303</v>
+      </c>
+      <c r="G12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12">
+        <v>1.459</v>
+      </c>
+      <c r="I12" s="1">
         <v>1.52</v>
       </c>
-      <c r="I9" s="1">
-        <v>15.2</v>
-      </c>
-      <c r="J9">
+      <c r="J12">
+        <v>50.62056</v>
+      </c>
+      <c r="K12" s="1">
         <v>1.55</v>
       </c>
-      <c r="K9" s="1">
-        <v>15.5</v>
-      </c>
-      <c r="L9" t="s">
-        <v>50</v>
-      </c>
-      <c r="M9">
-        <v>4100</v>
-      </c>
-      <c r="N9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10">
-        <v>24.81</v>
-      </c>
-      <c r="G10" t="s">
-        <v>42</v>
-      </c>
-      <c r="H10">
+      <c r="L12" s="1">
+        <v>51.61965</v>
+      </c>
+      <c r="M12" t="s">
+        <v>53</v>
+      </c>
+      <c r="N12">
+        <v>4163</v>
+      </c>
+      <c r="O12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13">
+        <v>16.568</v>
+      </c>
+      <c r="G13" t="s">
+        <v>43</v>
+      </c>
+      <c r="H13">
+        <v>1.459</v>
+      </c>
+      <c r="I13" s="1">
         <v>1.52</v>
       </c>
-      <c r="I10" s="1">
-        <v>37.71</v>
-      </c>
-      <c r="J10">
+      <c r="J13">
+        <v>25.18336</v>
+      </c>
+      <c r="K13" s="1">
         <v>1.55</v>
       </c>
-      <c r="K10" s="1">
-        <v>38.46</v>
-      </c>
-      <c r="L10" t="s">
-        <v>46</v>
-      </c>
-      <c r="M10">
-        <v>243034</v>
-      </c>
-      <c r="N10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="L13" s="1">
+        <v>25.6804</v>
+      </c>
+      <c r="M13" t="s">
+        <v>54</v>
+      </c>
+      <c r="N13">
+        <v>4953</v>
+      </c>
+      <c r="O13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" t="s">
         <v>41</v>
-      </c>
-      <c r="F11">
-        <v>21.84</v>
-      </c>
-      <c r="G11" t="s">
-        <v>42</v>
-      </c>
-      <c r="H11">
-        <v>1.74</v>
-      </c>
-      <c r="I11" s="1">
-        <v>38</v>
-      </c>
-      <c r="J11">
-        <v>1.77</v>
-      </c>
-      <c r="K11" s="1">
-        <v>38.66</v>
-      </c>
-      <c r="L11" t="s">
-        <v>51</v>
-      </c>
-      <c r="M11">
-        <v>55100</v>
-      </c>
-      <c r="N11" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F12">
-        <v>33.3</v>
-      </c>
-      <c r="G12" t="s">
-        <v>42</v>
-      </c>
-      <c r="H12">
-        <v>1.52</v>
-      </c>
-      <c r="I12" s="1">
-        <v>50.62</v>
-      </c>
-      <c r="J12">
-        <v>1.55</v>
-      </c>
-      <c r="K12" s="1">
-        <v>51.61</v>
-      </c>
-      <c r="L12" t="s">
-        <v>52</v>
-      </c>
-      <c r="M12">
-        <v>4163</v>
-      </c>
-      <c r="N12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13">
-        <v>16.57</v>
-      </c>
-      <c r="G13" t="s">
-        <v>42</v>
-      </c>
-      <c r="H13">
-        <v>1.52</v>
-      </c>
-      <c r="I13" s="1">
-        <v>25.19</v>
-      </c>
-      <c r="J13">
-        <v>1.55</v>
-      </c>
-      <c r="K13" s="1">
-        <v>25.68</v>
-      </c>
-      <c r="L13" t="s">
-        <v>53</v>
-      </c>
-      <c r="M13">
-        <v>4953</v>
-      </c>
-      <c r="N13" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14" t="s">
-        <v>40</v>
       </c>
       <c r="F14">
         <v>30.69</v>
       </c>
       <c r="G14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H14">
+        <v>1.459</v>
+      </c>
+      <c r="I14" s="1">
         <v>1.52</v>
       </c>
-      <c r="I14" s="1">
-        <v>46.65</v>
-      </c>
       <c r="J14">
+        <v>46.6488</v>
+      </c>
+      <c r="K14" s="1">
         <v>1.55</v>
       </c>
-      <c r="K14" s="1">
-        <v>47.57</v>
-      </c>
-      <c r="L14" t="s">
-        <v>54</v>
-      </c>
-      <c r="M14">
+      <c r="L14" s="1">
+        <v>47.5695</v>
+      </c>
+      <c r="M14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N14">
         <v>4840</v>
       </c>
-      <c r="N14" t="s">
-        <v>67</v>
+      <c r="O14" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -1282,56 +1327,56 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B19" s="6">
-        <v>299.13</v>
+        <v>299.142</v>
       </c>
       <c r="C19" s="6">
         <v>10</v>
       </c>
       <c r="D19" s="7">
-        <v>1.498345</v>
+        <v>1.498334</v>
       </c>
       <c r="E19" s="6">
-        <v>448.2</v>
+        <v>448.21</v>
       </c>
       <c r="F19" s="6">
-        <v>457.18</v>
+        <v>457.19</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B20" s="6">
-        <v>77.16</v>
+        <v>77.163</v>
       </c>
       <c r="C20" s="6">
         <v>2</v>
       </c>
       <c r="D20" s="7">
-        <v>1.67548</v>
+        <v>1.675476</v>
       </c>
       <c r="E20" s="6">
         <v>129.28</v>
@@ -1342,7 +1387,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B21" s="6">
         <v>20</v>
@@ -1362,20 +1407,20 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B22" s="9">
-        <v>396.29</v>
+        <v>396.305</v>
       </c>
       <c r="C22" s="9">
         <v>13</v>
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="9">
-        <v>612.48</v>
+        <v>612.49</v>
       </c>
       <c r="F22" s="9">
-        <v>624.38</v>
+        <v>624.39</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="74">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -246,8 +243,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -340,10 +337,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -638,7 +635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -651,13 +648,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -700,624 +697,582 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F2">
         <v>20</v>
       </c>
       <c r="G2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2">
+        <v>1.75</v>
+      </c>
+      <c r="I2" s="1">
+        <v>35</v>
+      </c>
+      <c r="J2">
+        <v>1.78</v>
+      </c>
+      <c r="K2" s="1">
+        <v>35.6</v>
+      </c>
+      <c r="L2" t="s">
         <v>43</v>
       </c>
-      <c r="H2">
-        <v>1.599</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="J2">
-        <v>35</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.78</v>
-      </c>
-      <c r="L2" s="1">
-        <v>35.6</v>
-      </c>
-      <c r="M2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="O2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F3">
         <v>40</v>
       </c>
       <c r="G3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H3">
-        <v>1.359</v>
+        <v>1.46</v>
       </c>
       <c r="I3" s="1">
-        <v>1.46</v>
+        <v>58.4</v>
       </c>
       <c r="J3">
-        <v>58.4</v>
+        <v>1.49</v>
       </c>
       <c r="K3" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L3" s="1">
         <v>59.6</v>
       </c>
-      <c r="M3" t="s">
-        <v>45</v>
-      </c>
-      <c r="N3">
+      <c r="L3" t="s">
+        <v>44</v>
+      </c>
+      <c r="M3">
         <v>4284</v>
       </c>
-      <c r="O3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F4">
         <v>38.852</v>
       </c>
       <c r="G4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H4">
-        <v>1.359</v>
+        <v>1.46</v>
       </c>
       <c r="I4" s="1">
-        <v>1.46</v>
+        <v>56.724</v>
       </c>
       <c r="J4">
-        <v>56.72392</v>
+        <v>1.49</v>
       </c>
       <c r="K4" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L4" s="1">
-        <v>57.88948</v>
-      </c>
-      <c r="M4" t="s">
-        <v>46</v>
-      </c>
-      <c r="N4">
+        <v>57.889</v>
+      </c>
+      <c r="L4" t="s">
+        <v>45</v>
+      </c>
+      <c r="M4">
         <v>3787</v>
       </c>
-      <c r="O4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F5">
         <v>41.682</v>
       </c>
       <c r="G5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H5">
-        <v>1.369</v>
+        <v>1.48</v>
       </c>
       <c r="I5" s="1">
-        <v>1.48</v>
+        <v>61.689</v>
       </c>
       <c r="J5">
-        <v>61.68936</v>
+        <v>1.51</v>
       </c>
       <c r="K5" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L5" s="1">
-        <v>62.93982</v>
-      </c>
-      <c r="M5" t="s">
-        <v>47</v>
-      </c>
-      <c r="N5">
+        <v>62.94</v>
+      </c>
+      <c r="L5" t="s">
+        <v>46</v>
+      </c>
+      <c r="M5">
         <v>4498</v>
       </c>
-      <c r="O5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="N5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F6">
         <v>35.753</v>
       </c>
       <c r="G6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H6">
-        <v>1.401</v>
+        <v>1.51</v>
       </c>
       <c r="I6" s="1">
-        <v>1.51</v>
+        <v>53.987</v>
       </c>
       <c r="J6">
-        <v>53.98703</v>
+        <v>1.54</v>
       </c>
       <c r="K6" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L6" s="1">
-        <v>55.05962</v>
-      </c>
-      <c r="M6" t="s">
-        <v>48</v>
-      </c>
-      <c r="N6">
+        <v>55.06</v>
+      </c>
+      <c r="L6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6">
         <v>4570</v>
       </c>
-      <c r="O6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="N6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F7">
         <v>55.321</v>
       </c>
       <c r="G7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H7">
-        <v>1.588</v>
+        <v>1.65</v>
       </c>
       <c r="I7" s="1">
-        <v>1.65</v>
+        <v>91.28</v>
       </c>
       <c r="J7">
-        <v>91.27965</v>
+        <v>1.68</v>
       </c>
       <c r="K7" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L7" s="1">
-        <v>92.93928</v>
-      </c>
-      <c r="M7" t="s">
-        <v>49</v>
-      </c>
-      <c r="N7">
+        <v>92.93899999999999</v>
+      </c>
+      <c r="L7" t="s">
+        <v>48</v>
+      </c>
+      <c r="M7">
         <v>54964</v>
       </c>
-      <c r="O7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="N7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F8">
         <v>27.481</v>
       </c>
       <c r="G8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H8">
-        <v>1.401</v>
+        <v>1.53</v>
       </c>
       <c r="I8" s="1">
-        <v>1.53</v>
+        <v>42.046</v>
       </c>
       <c r="J8">
-        <v>42.04593</v>
+        <v>1.56</v>
       </c>
       <c r="K8" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L8" s="1">
-        <v>42.87036</v>
-      </c>
-      <c r="M8" t="s">
-        <v>50</v>
-      </c>
-      <c r="N8">
+        <v>42.87</v>
+      </c>
+      <c r="L8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M8">
         <v>4780</v>
       </c>
-      <c r="O8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="N8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F9">
         <v>10</v>
       </c>
       <c r="G9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H9">
-        <v>1.449</v>
+        <v>1.52</v>
       </c>
       <c r="I9" s="1">
-        <v>1.52</v>
+        <v>15.2</v>
       </c>
       <c r="J9">
-        <v>15.2</v>
+        <v>1.55</v>
       </c>
       <c r="K9" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L9" s="1">
         <v>15.5</v>
       </c>
-      <c r="M9" t="s">
-        <v>51</v>
-      </c>
-      <c r="N9">
+      <c r="L9" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9">
         <v>4100</v>
       </c>
-      <c r="O9" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="N9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F10">
         <v>24.813</v>
       </c>
       <c r="G10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H10">
-        <v>1.459</v>
+        <v>1.52</v>
       </c>
       <c r="I10" s="1">
-        <v>1.52</v>
+        <v>37.716</v>
       </c>
       <c r="J10">
-        <v>37.71576</v>
+        <v>1.55</v>
       </c>
       <c r="K10" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L10" s="1">
-        <v>38.46015</v>
-      </c>
-      <c r="M10" t="s">
-        <v>47</v>
-      </c>
-      <c r="N10">
+        <v>38.46</v>
+      </c>
+      <c r="L10" t="s">
+        <v>46</v>
+      </c>
+      <c r="M10">
         <v>243034</v>
       </c>
-      <c r="O10" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="N10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F11">
         <v>21.842</v>
       </c>
       <c r="G11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H11">
-        <v>1.689</v>
+        <v>1.74</v>
       </c>
       <c r="I11" s="1">
-        <v>1.74</v>
+        <v>38.005</v>
       </c>
       <c r="J11">
-        <v>38.00508</v>
+        <v>1.77</v>
       </c>
       <c r="K11" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L11" s="1">
-        <v>38.66034</v>
-      </c>
-      <c r="M11" t="s">
-        <v>52</v>
-      </c>
-      <c r="N11">
+        <v>38.66</v>
+      </c>
+      <c r="L11" t="s">
+        <v>51</v>
+      </c>
+      <c r="M11">
         <v>55100</v>
       </c>
-      <c r="O11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="N11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F12">
         <v>33.303</v>
       </c>
       <c r="G12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H12">
-        <v>1.459</v>
+        <v>1.52</v>
       </c>
       <c r="I12" s="1">
-        <v>1.52</v>
+        <v>50.621</v>
       </c>
       <c r="J12">
-        <v>50.62056</v>
+        <v>1.55</v>
       </c>
       <c r="K12" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L12" s="1">
-        <v>51.61965</v>
-      </c>
-      <c r="M12" t="s">
-        <v>53</v>
-      </c>
-      <c r="N12">
+        <v>51.62</v>
+      </c>
+      <c r="L12" t="s">
+        <v>52</v>
+      </c>
+      <c r="M12">
         <v>4163</v>
       </c>
-      <c r="O12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+      <c r="N12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F13">
         <v>16.568</v>
       </c>
       <c r="G13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H13">
-        <v>1.459</v>
+        <v>1.52</v>
       </c>
       <c r="I13" s="1">
-        <v>1.52</v>
+        <v>25.183</v>
       </c>
       <c r="J13">
-        <v>25.18336</v>
+        <v>1.55</v>
       </c>
       <c r="K13" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L13" s="1">
-        <v>25.6804</v>
-      </c>
-      <c r="M13" t="s">
-        <v>54</v>
-      </c>
-      <c r="N13">
+        <v>25.68</v>
+      </c>
+      <c r="L13" t="s">
+        <v>53</v>
+      </c>
+      <c r="M13">
         <v>4953</v>
       </c>
-      <c r="O13" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+      <c r="N13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F14">
         <v>30.69</v>
       </c>
       <c r="G14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H14">
-        <v>1.459</v>
+        <v>1.52</v>
       </c>
       <c r="I14" s="1">
-        <v>1.52</v>
+        <v>46.649</v>
       </c>
       <c r="J14">
-        <v>46.6488</v>
+        <v>1.55</v>
       </c>
       <c r="K14" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L14" s="1">
-        <v>47.5695</v>
-      </c>
-      <c r="M14" t="s">
-        <v>55</v>
-      </c>
-      <c r="N14">
+        <v>47.57</v>
+      </c>
+      <c r="L14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M14">
         <v>4840</v>
       </c>
-      <c r="O14" t="s">
-        <v>68</v>
+      <c r="N14" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -1327,87 +1282,87 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="C18" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="D18" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>73</v>
-      </c>
       <c r="E18" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B19" s="6">
         <v>299.142</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="7">
         <v>10</v>
       </c>
       <c r="D19" s="7">
-        <v>1.498334</v>
-      </c>
-      <c r="E19" s="6">
-        <v>448.21</v>
-      </c>
-      <c r="F19" s="6">
-        <v>457.19</v>
+        <v>1.498</v>
+      </c>
+      <c r="E19" s="7">
+        <v>448.215</v>
+      </c>
+      <c r="F19" s="7">
+        <v>457.189</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B20" s="6">
         <v>77.163</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="7">
         <v>2</v>
       </c>
       <c r="D20" s="7">
-        <v>1.675476</v>
-      </c>
-      <c r="E20" s="6">
-        <v>129.28</v>
-      </c>
-      <c r="F20" s="6">
-        <v>131.6</v>
+        <v>1.675</v>
+      </c>
+      <c r="E20" s="7">
+        <v>129.285</v>
+      </c>
+      <c r="F20" s="7">
+        <v>131.599</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B21" s="6">
         <v>20</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="7">
         <v>1</v>
       </c>
       <c r="D21" s="7">
         <v>1.75</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="7">
         <v>35</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F21" s="7">
         <v>35.6</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B22" s="9">
         <v>396.305</v>
@@ -1417,10 +1372,10 @@
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="9">
-        <v>612.49</v>
+        <v>612.5</v>
       </c>
       <c r="F22" s="9">
-        <v>624.39</v>
+        <v>624.388</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="77">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -64,52 +67,166 @@
     <t>2026-08-13</t>
   </si>
   <si>
-    <t>Варна Цар Освободител</t>
-  </si>
-  <si>
-    <t>Варна Сливница</t>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-08-19</t>
+  </si>
+  <si>
+    <t>2026-08-21</t>
+  </si>
+  <si>
+    <t>2026-08-24</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>В4603ХК</t>
   </si>
   <si>
     <t>ТубаДДД6</t>
   </si>
   <si>
-    <t>В4603ХК</t>
-  </si>
-  <si>
     <t>В4601ХК</t>
   </si>
   <si>
     <t>В4602ХК</t>
   </si>
   <si>
+    <t>ТубаДДД5</t>
+  </si>
+  <si>
+    <t>ТубаДДД4</t>
+  </si>
+  <si>
+    <t>В2658НА</t>
+  </si>
+  <si>
+    <t>78970155027720402</t>
+  </si>
+  <si>
     <t>78970155027720485</t>
   </si>
   <si>
-    <t>78970155027720402</t>
-  </si>
-  <si>
     <t>78970155027720386</t>
   </si>
   <si>
     <t>78970155027720394</t>
   </si>
   <si>
+    <t>78970155027720477</t>
+  </si>
+  <si>
+    <t>78970155027720469</t>
+  </si>
+  <si>
+    <t>78970155027720410</t>
+  </si>
+  <si>
+    <t>95 EKONOMY UNLEADED</t>
+  </si>
+  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
-    <t>16:18</t>
-  </si>
-  <si>
-    <t>16:21</t>
-  </si>
-  <si>
-    <t>07:54</t>
-  </si>
-  <si>
-    <t>08:19</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>16:20:00</t>
+  </si>
+  <si>
+    <t>16:17:00</t>
+  </si>
+  <si>
+    <t>07:54:00</t>
+  </si>
+  <si>
+    <t>08:19:00</t>
+  </si>
+  <si>
+    <t>14:18:00</t>
+  </si>
+  <si>
+    <t>11:03:00</t>
+  </si>
+  <si>
+    <t>09:40:00</t>
+  </si>
+  <si>
+    <t>07:59:00</t>
+  </si>
+  <si>
+    <t>10:39:00</t>
+  </si>
+  <si>
+    <t>08:06:00</t>
+  </si>
+  <si>
+    <t>14:12:00</t>
+  </si>
+  <si>
+    <t>07:24:00</t>
+  </si>
+  <si>
+    <t>10:42:00</t>
+  </si>
+  <si>
+    <t>3235959597 3235959597</t>
+  </si>
+  <si>
+    <t>3235960832 3235960832</t>
+  </si>
+  <si>
+    <t>3236186811 3236186811</t>
+  </si>
+  <si>
+    <t>3236283899 3236283899</t>
+  </si>
+  <si>
+    <t>3236532488 3236532488</t>
+  </si>
+  <si>
+    <t>3236594222 3236594222</t>
+  </si>
+  <si>
+    <t>3236715901 3236715901</t>
+  </si>
+  <si>
+    <t>3236848463 3236848463</t>
+  </si>
+  <si>
+    <t>3236956210 3236956210</t>
+  </si>
+  <si>
+    <t>3237185528 3237185528</t>
+  </si>
+  <si>
+    <t>3237187462 3237187462</t>
+  </si>
+  <si>
+    <t>3237207817 3237207817</t>
+  </si>
+  <si>
+    <t>3237213245 3237213245</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ</t>
@@ -134,9 +251,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00000"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -216,7 +334,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -229,10 +347,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -527,7 +647,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -536,16 +656,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -585,262 +706,673 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2">
+        <v>22.72</v>
+      </c>
+      <c r="G2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" s="1">
+        <v>1.429</v>
+      </c>
+      <c r="I2" s="1">
+        <v>32.467</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="K2" s="1">
+        <v>35.216</v>
+      </c>
+      <c r="L2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M2">
+        <v>5141</v>
+      </c>
+      <c r="N2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3">
+        <v>12.78</v>
+      </c>
+      <c r="G3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1.677</v>
+      </c>
+      <c r="I3" s="1">
+        <v>21.432</v>
+      </c>
+      <c r="J3" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="K3" s="1">
+        <v>23.004</v>
+      </c>
+      <c r="L3" t="s">
+        <v>46</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4">
+        <v>33.36</v>
+      </c>
+      <c r="G4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1.409</v>
+      </c>
+      <c r="I4" s="1">
+        <v>47.004</v>
+      </c>
+      <c r="J4" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="K4" s="1">
+        <v>51.708</v>
+      </c>
+      <c r="L4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M4">
+        <v>4499</v>
+      </c>
+      <c r="N4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5">
+        <v>41.77</v>
+      </c>
+      <c r="G5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1.409</v>
+      </c>
+      <c r="I5" s="1">
+        <v>58.854</v>
+      </c>
+      <c r="J5" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="K5" s="1">
+        <v>64.744</v>
+      </c>
+      <c r="L5" t="s">
+        <v>48</v>
+      </c>
+      <c r="M5">
+        <v>5152</v>
+      </c>
+      <c r="N5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6">
+        <v>31.37</v>
+      </c>
+      <c r="G6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1.429</v>
+      </c>
+      <c r="I6" s="1">
+        <v>44.828</v>
+      </c>
+      <c r="J6" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="K6" s="1">
+        <v>48.937</v>
+      </c>
+      <c r="L6" t="s">
+        <v>49</v>
+      </c>
+      <c r="M6">
+        <v>5470</v>
+      </c>
+      <c r="N6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7">
+        <v>10.01</v>
+      </c>
+      <c r="G7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1.677</v>
+      </c>
+      <c r="I7" s="1">
+        <v>16.787</v>
+      </c>
+      <c r="J7" s="1">
+        <v>1.82</v>
+      </c>
+      <c r="K7" s="1">
+        <v>18.218</v>
+      </c>
+      <c r="L7" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8">
+        <v>38.7</v>
+      </c>
+      <c r="G8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1.429</v>
+      </c>
+      <c r="I8" s="1">
+        <v>55.302</v>
+      </c>
+      <c r="J8" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="K8" s="1">
+        <v>60.759</v>
+      </c>
+      <c r="L8" t="s">
+        <v>51</v>
+      </c>
+      <c r="M8">
+        <v>5500</v>
+      </c>
+      <c r="N8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9">
+        <v>17.15</v>
+      </c>
+      <c r="G9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1.708</v>
+      </c>
+      <c r="I9" s="1">
+        <v>29.292</v>
+      </c>
+      <c r="J9" s="1">
+        <v>1.85</v>
+      </c>
+      <c r="K9" s="1">
+        <v>31.728</v>
+      </c>
+      <c r="L9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10">
+        <v>34.68</v>
+      </c>
+      <c r="G10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1.459</v>
+      </c>
+      <c r="I10" s="1">
+        <v>50.598</v>
+      </c>
+      <c r="J10" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="K10" s="1">
+        <v>54.794</v>
+      </c>
+      <c r="L10" t="s">
+        <v>53</v>
+      </c>
+      <c r="M10">
+        <v>5850</v>
+      </c>
+      <c r="N10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11">
+        <v>27.19</v>
+      </c>
+      <c r="G11" t="s">
+        <v>44</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1.459</v>
+      </c>
+      <c r="I11" s="1">
+        <v>39.67</v>
+      </c>
+      <c r="J11" s="1">
+        <v>1.61</v>
+      </c>
+      <c r="K11" s="1">
+        <v>43.776</v>
+      </c>
+      <c r="L11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M11">
+        <v>5700</v>
+      </c>
+      <c r="N11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12">
+        <v>15</v>
+      </c>
+      <c r="G12" t="s">
+        <v>44</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1.459</v>
+      </c>
+      <c r="I12" s="1">
+        <v>21.885</v>
+      </c>
+      <c r="J12" s="1">
+        <v>1.61</v>
+      </c>
+      <c r="K12" s="1">
+        <v>24.15</v>
+      </c>
+      <c r="L12" t="s">
+        <v>55</v>
+      </c>
+      <c r="M12">
+        <v>243130</v>
+      </c>
+      <c r="N12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13">
+        <v>38.87</v>
+      </c>
+      <c r="G13" t="s">
+        <v>44</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1.459</v>
+      </c>
+      <c r="I13" s="1">
+        <v>56.711</v>
+      </c>
+      <c r="J13" s="1">
+        <v>1.61</v>
+      </c>
+      <c r="K13" s="1">
+        <v>62.581</v>
+      </c>
+      <c r="L13" t="s">
+        <v>56</v>
+      </c>
+      <c r="M13">
+        <v>4959</v>
+      </c>
+      <c r="N13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14">
+        <v>16.86</v>
+      </c>
+      <c r="G14" t="s">
+        <v>44</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1.459</v>
+      </c>
+      <c r="I14" s="1">
+        <v>24.599</v>
+      </c>
+      <c r="J14" s="1">
+        <v>1.61</v>
+      </c>
+      <c r="K14" s="1">
+        <v>27.145</v>
+      </c>
+      <c r="L14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M14">
+        <v>6018</v>
+      </c>
+      <c r="N14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="6">
+        <v>300.52</v>
+      </c>
+      <c r="C19" s="7">
+        <v>10</v>
+      </c>
+      <c r="D19" s="8">
+        <v>1.43724</v>
+      </c>
+      <c r="E19" s="6">
+        <v>431.92</v>
+      </c>
+      <c r="F19" s="6">
+        <v>473.81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="6">
+        <v>39.94</v>
+      </c>
+      <c r="C20" s="7">
+        <v>3</v>
+      </c>
+      <c r="D20" s="8">
+        <v>1.69031</v>
+      </c>
+      <c r="E20" s="6">
+        <v>67.51000000000001</v>
+      </c>
+      <c r="F20" s="6">
+        <v>72.95</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B21" s="10">
+        <v>340.46</v>
+      </c>
+      <c r="C21" s="11">
         <v>13</v>
       </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2">
-        <v>12.778</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="H2">
-        <v>22.617</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="J2">
-        <v>23</v>
-      </c>
-      <c r="K2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>290050</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3">
-        <v>22.723</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="H3">
-        <v>34.539</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="J3">
-        <v>35.221</v>
-      </c>
-      <c r="K3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3">
-        <v>5141</v>
-      </c>
-      <c r="M3">
-        <v>290054</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4">
-        <v>33.361</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="H4">
-        <v>50.709</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="J4">
-        <v>51.71</v>
-      </c>
-      <c r="K4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L4">
-        <v>4499</v>
-      </c>
-      <c r="M4">
-        <v>161857</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5">
-        <v>41.768</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="H5">
-        <v>63.487</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="J5">
-        <v>64.73999999999999</v>
-      </c>
-      <c r="K5" t="s">
-        <v>31</v>
-      </c>
-      <c r="L5">
-        <v>5152</v>
-      </c>
-      <c r="M5">
-        <v>162743</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="6">
-        <v>97.852</v>
-      </c>
-      <c r="C10" s="6">
-        <v>3</v>
-      </c>
-      <c r="D10" s="7">
-        <v>1.52</v>
-      </c>
-      <c r="E10" s="6">
-        <v>148.74</v>
-      </c>
-      <c r="F10" s="6">
-        <v>151.671</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="6">
-        <v>12.778</v>
-      </c>
-      <c r="C11" s="6">
-        <v>1</v>
-      </c>
-      <c r="D11" s="7">
-        <v>1.77</v>
-      </c>
-      <c r="E11" s="6">
-        <v>22.62</v>
-      </c>
-      <c r="F11" s="6">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="9">
-        <v>110.63</v>
-      </c>
-      <c r="C12" s="9">
-        <v>4</v>
-      </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="9">
-        <v>171.36</v>
-      </c>
-      <c r="F12" s="9">
-        <v>174.671</v>
+      <c r="D21" s="8"/>
+      <c r="E21" s="10">
+        <v>499.43</v>
+      </c>
+      <c r="F21" s="10">
+        <v>546.76</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A17:F17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ/ОП ДЕЗИНФЕКЦИЯ, ДЕЗИНСЕКЦИЯ, ДЕРАТИЗАЦИЯ.xlsx
@@ -733,10 +733,10 @@
         <v>44</v>
       </c>
       <c r="H2" s="1">
-        <v>1.429</v>
+        <v>1.52</v>
       </c>
       <c r="I2" s="1">
-        <v>32.467</v>
+        <v>34.534</v>
       </c>
       <c r="J2" s="1">
         <v>1.55</v>
@@ -777,10 +777,10 @@
         <v>44</v>
       </c>
       <c r="H3" s="1">
-        <v>1.677</v>
+        <v>1.77</v>
       </c>
       <c r="I3" s="1">
-        <v>21.432</v>
+        <v>22.621</v>
       </c>
       <c r="J3" s="1">
         <v>1.8</v>
@@ -821,10 +821,10 @@
         <v>44</v>
       </c>
       <c r="H4" s="1">
-        <v>1.409</v>
+        <v>1.52</v>
       </c>
       <c r="I4" s="1">
-        <v>47.004</v>
+        <v>50.707</v>
       </c>
       <c r="J4" s="1">
         <v>1.55</v>
@@ -865,10 +865,10 @@
         <v>44</v>
       </c>
       <c r="H5" s="1">
-        <v>1.409</v>
+        <v>1.52</v>
       </c>
       <c r="I5" s="1">
-        <v>58.854</v>
+        <v>63.49</v>
       </c>
       <c r="J5" s="1">
         <v>1.55</v>
@@ -909,10 +909,10 @@
         <v>44</v>
       </c>
       <c r="H6" s="1">
-        <v>1.429</v>
+        <v>1.53</v>
       </c>
       <c r="I6" s="1">
-        <v>44.828</v>
+        <v>47.996</v>
       </c>
       <c r="J6" s="1">
         <v>1.56</v>
@@ -953,10 +953,10 @@
         <v>44</v>
       </c>
       <c r="H7" s="1">
-        <v>1.677</v>
+        <v>1.79</v>
       </c>
       <c r="I7" s="1">
-        <v>16.787</v>
+        <v>17.918</v>
       </c>
       <c r="J7" s="1">
         <v>1.82</v>
@@ -997,10 +997,10 @@
         <v>44</v>
       </c>
       <c r="H8" s="1">
-        <v>1.429</v>
+        <v>1.54</v>
       </c>
       <c r="I8" s="1">
-        <v>55.302</v>
+        <v>59.598</v>
       </c>
       <c r="J8" s="1">
         <v>1.57</v>
@@ -1041,10 +1041,10 @@
         <v>44</v>
       </c>
       <c r="H9" s="1">
-        <v>1.708</v>
+        <v>1.82</v>
       </c>
       <c r="I9" s="1">
-        <v>29.292</v>
+        <v>31.213</v>
       </c>
       <c r="J9" s="1">
         <v>1.85</v>
@@ -1085,10 +1085,10 @@
         <v>44</v>
       </c>
       <c r="H10" s="1">
-        <v>1.459</v>
+        <v>1.55</v>
       </c>
       <c r="I10" s="1">
-        <v>50.598</v>
+        <v>53.754</v>
       </c>
       <c r="J10" s="1">
         <v>1.58</v>
@@ -1129,10 +1129,10 @@
         <v>44</v>
       </c>
       <c r="H11" s="1">
-        <v>1.459</v>
+        <v>1.58</v>
       </c>
       <c r="I11" s="1">
-        <v>39.67</v>
+        <v>42.96</v>
       </c>
       <c r="J11" s="1">
         <v>1.61</v>
@@ -1173,10 +1173,10 @@
         <v>44</v>
       </c>
       <c r="H12" s="1">
-        <v>1.459</v>
+        <v>1.58</v>
       </c>
       <c r="I12" s="1">
-        <v>21.885</v>
+        <v>23.7</v>
       </c>
       <c r="J12" s="1">
         <v>1.61</v>
@@ -1217,10 +1217,10 @@
         <v>44</v>
       </c>
       <c r="H13" s="1">
-        <v>1.459</v>
+        <v>1.58</v>
       </c>
       <c r="I13" s="1">
-        <v>56.711</v>
+        <v>61.415</v>
       </c>
       <c r="J13" s="1">
         <v>1.61</v>
@@ -1261,10 +1261,10 @@
         <v>44</v>
       </c>
       <c r="H14" s="1">
-        <v>1.459</v>
+        <v>1.58</v>
       </c>
       <c r="I14" s="1">
-        <v>24.599</v>
+        <v>26.639</v>
       </c>
       <c r="J14" s="1">
         <v>1.61</v>
@@ -1323,10 +1323,10 @@
         <v>10</v>
       </c>
       <c r="D19" s="8">
-        <v>1.43724</v>
+        <v>1.54663</v>
       </c>
       <c r="E19" s="6">
-        <v>431.92</v>
+        <v>464.79</v>
       </c>
       <c r="F19" s="6">
         <v>473.81</v>
@@ -1343,10 +1343,10 @@
         <v>3</v>
       </c>
       <c r="D20" s="8">
-        <v>1.69031</v>
+        <v>1.79649</v>
       </c>
       <c r="E20" s="6">
-        <v>67.51000000000001</v>
+        <v>71.75</v>
       </c>
       <c r="F20" s="6">
         <v>72.95</v>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="10">
-        <v>499.43</v>
+        <v>536.54</v>
       </c>
       <c r="F21" s="10">
         <v>546.76</v>
